--- a/Memoria/library/mediciones auxiliares.xlsx
+++ b/Memoria/library/mediciones auxiliares.xlsx
@@ -5,17 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\Fuera del repo TFG\Graficas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\TFG\Memoria\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCEE633-97E9-4D30-9BF0-51C1A3C21C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80340FEC-BBD7-433B-9D96-6C5373411089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Euler" sheetId="3" r:id="rId1"/>
-    <sheet name="Brusselator1D" sheetId="1" r:id="rId2"/>
-    <sheet name="Br2DABM" sheetId="2" r:id="rId3"/>
+    <sheet name="OMP-Br1d" sheetId="1" r:id="rId2"/>
+    <sheet name="OMP-Br2d" sheetId="2" r:id="rId3"/>
+    <sheet name="CUDA-Br2d" sheetId="4" r:id="rId4"/>
+    <sheet name="CUDA-tams" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
   <si>
     <t>Runge Kutta</t>
   </si>
@@ -117,12 +119,120 @@
   <si>
     <t>Comparativa entre aproximar con euler explicito y valor real</t>
   </si>
+  <si>
+    <t>CUDA</t>
+  </si>
+  <si>
+    <t>OMP</t>
+  </si>
+  <si>
+    <t>Comparamos sec + OMP + cuda con BR2D y 125K</t>
+  </si>
+  <si>
+    <t>Secuencial</t>
+  </si>
+  <si>
+    <t>ms/eq</t>
+  </si>
+  <si>
+    <t>neqn2</t>
+  </si>
+  <si>
+    <t>T (s)3</t>
+  </si>
+  <si>
+    <t>ms/eq4</t>
+  </si>
+  <si>
+    <t>neqn5</t>
+  </si>
+  <si>
+    <t>T (s)6</t>
+  </si>
+  <si>
+    <t>ms/eq7</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>4K</t>
+  </si>
+  <si>
+    <t>20K</t>
+  </si>
+  <si>
+    <t>30K</t>
+  </si>
+  <si>
+    <t>40K</t>
+  </si>
+  <si>
+    <t>60K</t>
+  </si>
+  <si>
+    <t>80K</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>150K</t>
+  </si>
+  <si>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>250K</t>
+  </si>
+  <si>
+    <t>300K</t>
+  </si>
+  <si>
+    <t>400K</t>
+  </si>
+  <si>
+    <t>350K</t>
+  </si>
+  <si>
+    <t>500K</t>
+  </si>
+  <si>
+    <t>600K</t>
+  </si>
+  <si>
+    <t>700K</t>
+  </si>
+  <si>
+    <t>800K</t>
+  </si>
+  <si>
+    <t>900K</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>1.5M</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>Comparo RK y BR1D a través de distintos tamaños</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +250,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -238,7 +356,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -252,13 +370,335 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{894E2A58-4AB2-4DD0-992A-D8EFC287A90D}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F071A7C7-C907-4782-97BC-1691119DD71E}"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -550,130 +990,6 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3308,7 +3624,7 @@
     <tableColumn id="7" xr3:uid="{64FA0956-3E24-4150-B966-D174B7BC073B}" name="Hebras"/>
     <tableColumn id="10" xr3:uid="{1B8321A3-89E7-440F-AC38-60832AF9D3BF}" name="T (s)"/>
     <tableColumn id="4" xr3:uid="{2A319FA1-3453-4EE4-B2DC-4F5247C2B6CA}" name="Speedup"/>
-    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="12">
+    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="30">
       <calculatedColumnFormula>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3317,18 +3633,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="29">
   <autoFilter ref="A17:F23" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:D23">
     <sortCondition descending="1" ref="D17:D23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="25"/>
     <tableColumn id="5" xr3:uid="{BF613CE6-6DEF-4C0B-848D-8F065FCF2C50}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="24">
       <calculatedColumnFormula>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3337,18 +3653,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="23">
   <autoFilter ref="A9:F15" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:D15">
     <sortCondition descending="1" ref="D9:D15"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{417AEB65-89EB-4AD8-BE23-D32970ABEDB3}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="18">
       <calculatedColumnFormula>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3368,7 +3684,7 @@
     <tableColumn id="3" xr3:uid="{3A3C5E88-C7DA-483A-917E-BB271E1A560D}" name="Tipo"/>
     <tableColumn id="10" xr3:uid="{16A7936E-BB2A-4361-A80F-5CD098124D72}" name="T (s)"/>
     <tableColumn id="1" xr3:uid="{99669171-F1C7-4284-B05F-40B0C07B15FF}" name="Speedup"/>
-    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="21">
+    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="17">
       <calculatedColumnFormula>Tabla2[[#This Row],[Speedup]]/Tabla2[[#This Row],[Hebras]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3377,16 +3693,65 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="K3:O12" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="9">
       <calculatedColumnFormula>Tabla3[[#This Row],[Speedup]]/Tabla3[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED7CDD12-53B9-478E-8FA6-1644F23C7700}" name="Tabla6" displayName="Tabla6" ref="D3:G12" totalsRowShown="0">
+  <autoFilter ref="D3:G12" xr:uid="{ED7CDD12-53B9-478E-8FA6-1644F23C7700}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D4:F12">
+    <sortCondition descending="1" ref="F3:F12"/>
+  </sortState>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F6A3A73A-53CD-4476-97D7-144BCC3C3B36}" name="Solver"/>
+    <tableColumn id="3" xr3:uid="{841090C2-3A84-47CB-ABE5-DAD379E7BEC5}" name="Tipo"/>
+    <tableColumn id="10" xr3:uid="{2A5DC087-1C05-46B6-893C-A16031247331}" name="T (s)"/>
+    <tableColumn id="12" xr3:uid="{D1A04DFE-7852-45ED-9D0C-6DDEEAD868F6}" name="Speedup"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}" name="Tabla7" displayName="Tabla7" ref="B3:E68" totalsRowShown="0">
+  <autoFilter ref="B3:E68" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{644F7757-56D6-4333-9A04-BB025A3FA537}" name="Solver"/>
+    <tableColumn id="9" xr3:uid="{7A4B951A-072B-4FA9-BB96-812FB6E68533}" name="neqn"/>
+    <tableColumn id="10" xr3:uid="{27844286-B464-4C11-8051-BCFF52593894}" name="T (s)"/>
+    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="8">
+      <calculatedColumnFormula>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="0">
+  <autoFilter ref="H3:P12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{932C3C52-A732-48FA-B5C5-2E96D1AF7393}" name="neqn"/>
+    <tableColumn id="2" xr3:uid="{180E0420-BB3F-4A15-AA9C-8504B61074B7}" name="T (s)"/>
+    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3703,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <f>ABS(D5-E5)</f>
+        <f t="shared" ref="F5:F15" si="0">ABS(D5-E5)</f>
         <v>0</v>
       </c>
       <c r="G5">
@@ -3716,19 +4081,19 @@
         <v>0.1</v>
       </c>
       <c r="D6">
-        <f>D5+$I$2*(-2*D5)</f>
+        <f t="shared" ref="D6:D15" si="1">D5+$I$2*(-2*D5)</f>
         <v>0.8</v>
       </c>
       <c r="E6">
-        <f>EXP(-2*C6)</f>
+        <f t="shared" ref="E6:E15" si="2">EXP(-2*C6)</f>
         <v>0.81873075307798182</v>
       </c>
       <c r="F6">
-        <f>ABS(D6-E6)</f>
+        <f t="shared" si="0"/>
         <v>1.8730753077981777E-2</v>
       </c>
       <c r="G6">
-        <f>(F6/E6)*100</f>
+        <f t="shared" ref="G6:G15" si="3">(F6/E6)*100</f>
         <v>2.2877793471864036</v>
       </c>
     </row>
@@ -3737,19 +4102,19 @@
         <v>0.2</v>
       </c>
       <c r="D7">
-        <f>D6+$I$2*(-2*D6)</f>
+        <f t="shared" si="1"/>
         <v>0.64</v>
       </c>
       <c r="E7">
-        <f>EXP(-2*C7)</f>
+        <f t="shared" si="2"/>
         <v>0.67032004603563933</v>
       </c>
       <c r="F7">
-        <f>ABS(D7-E7)</f>
+        <f t="shared" si="0"/>
         <v>3.0320046035639314E-2</v>
       </c>
       <c r="G7">
-        <f>(F7/E7)*100</f>
+        <f t="shared" si="3"/>
         <v>4.5232193509587013</v>
       </c>
     </row>
@@ -3758,19 +4123,19 @@
         <v>0.3</v>
       </c>
       <c r="D8">
-        <f>D7+$I$2*(-2*D7)</f>
+        <f t="shared" si="1"/>
         <v>0.51200000000000001</v>
       </c>
       <c r="E8">
-        <f>EXP(-2*C8)</f>
+        <f t="shared" si="2"/>
         <v>0.54881163609402639</v>
       </c>
       <c r="F8">
-        <f>ABS(D8-E8)</f>
+        <f t="shared" si="0"/>
         <v>3.6811636094026379E-2</v>
       </c>
       <c r="G8">
-        <f>(F8/E8)*100</f>
+        <f t="shared" si="3"/>
         <v>6.7075174200059315</v>
       </c>
     </row>
@@ -3779,19 +4144,19 @@
         <v>0.4</v>
       </c>
       <c r="D9">
-        <f>D8+$I$2*(-2*D8)</f>
+        <f t="shared" si="1"/>
         <v>0.40960000000000002</v>
       </c>
       <c r="E9">
-        <f>EXP(-2*C9)</f>
+        <f t="shared" si="2"/>
         <v>0.44932896411722156</v>
       </c>
       <c r="F9">
-        <f>ABS(D9-E9)</f>
+        <f t="shared" si="0"/>
         <v>3.9728964117221544E-2</v>
       </c>
       <c r="G9">
-        <f>(F9/E9)*100</f>
+        <f t="shared" si="3"/>
         <v>8.8418435689485175</v>
       </c>
     </row>
@@ -3800,19 +4165,19 @@
         <v>0.5</v>
       </c>
       <c r="D10">
-        <f>D9+$I$2*(-2*D9)</f>
+        <f t="shared" si="1"/>
         <v>0.32768000000000003</v>
       </c>
       <c r="E10">
-        <f>EXP(-2*C10)</f>
+        <f t="shared" si="2"/>
         <v>0.36787944117144233</v>
       </c>
       <c r="F10">
-        <f>ABS(D10-E10)</f>
+        <f t="shared" si="0"/>
         <v>4.0199441171442307E-2</v>
       </c>
       <c r="G10">
-        <f>(F10/E10)*100</f>
+        <f t="shared" si="3"/>
         <v>10.927341045054002</v>
       </c>
     </row>
@@ -3821,19 +4186,19 @@
         <v>0.6</v>
       </c>
       <c r="D11">
-        <f>D10+$I$2*(-2*D10)</f>
+        <f t="shared" si="1"/>
         <v>0.26214400000000004</v>
       </c>
       <c r="E11">
-        <f>EXP(-2*C11)</f>
+        <f t="shared" si="2"/>
         <v>0.30119421191220214</v>
       </c>
       <c r="F11">
-        <f>ABS(D11-E11)</f>
+        <f t="shared" si="0"/>
         <v>3.9050211912202093E-2</v>
       </c>
       <c r="G11">
-        <f>(F11/E11)*100</f>
+        <f t="shared" si="3"/>
         <v>12.965126940615047</v>
       </c>
     </row>
@@ -3842,19 +4207,19 @@
         <v>0.7</v>
       </c>
       <c r="D12">
-        <f>D11+$I$2*(-2*D11)</f>
+        <f t="shared" si="1"/>
         <v>0.20971520000000005</v>
       </c>
       <c r="E12">
-        <f>EXP(-2*C12)</f>
+        <f t="shared" si="2"/>
         <v>0.24659696394160649</v>
       </c>
       <c r="F12">
-        <f>ABS(D12-E12)</f>
+        <f t="shared" si="0"/>
         <v>3.6881763941606444E-2</v>
       </c>
       <c r="G12">
-        <f>(F12/E12)*100</f>
+        <f t="shared" si="3"/>
         <v>14.956292791317555</v>
       </c>
     </row>
@@ -3863,19 +4228,19 @@
         <v>0.8</v>
       </c>
       <c r="D13">
-        <f>D12+$I$2*(-2*D12)</f>
+        <f t="shared" si="1"/>
         <v>0.16777216000000003</v>
       </c>
       <c r="E13">
-        <f>EXP(-2*C13)</f>
+        <f t="shared" si="2"/>
         <v>0.20189651799465538</v>
       </c>
       <c r="F13">
-        <f>ABS(D13-E13)</f>
+        <f t="shared" si="0"/>
         <v>3.4124357994655352E-2</v>
       </c>
       <c r="G13">
-        <f>(F13/E13)*100</f>
+        <f t="shared" si="3"/>
         <v>16.901905160919465</v>
       </c>
     </row>
@@ -3884,19 +4249,19 @@
         <v>0.9</v>
       </c>
       <c r="D14">
-        <f>D13+$I$2*(-2*D13)</f>
+        <f t="shared" si="1"/>
         <v>0.13421772800000004</v>
       </c>
       <c r="E14">
-        <f>EXP(-2*C14)</f>
+        <f t="shared" si="2"/>
         <v>0.16529888822158653</v>
       </c>
       <c r="F14">
-        <f>ABS(D14-E14)</f>
+        <f t="shared" si="0"/>
         <v>3.1081160221586496E-2</v>
       </c>
       <c r="G14">
-        <f>(F14/E14)*100</f>
+        <f t="shared" si="3"/>
         <v>18.803006212553328</v>
       </c>
     </row>
@@ -3905,19 +4270,19 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <f>D14+$I$2*(-2*D14)</f>
+        <f t="shared" si="1"/>
         <v>0.10737418240000003</v>
       </c>
       <c r="E15">
-        <f>EXP(-2*C15)</f>
+        <f t="shared" si="2"/>
         <v>0.1353352832366127</v>
       </c>
       <c r="F15">
-        <f>ABS(D15-E15)</f>
+        <f t="shared" si="0"/>
         <v>2.7961100836612671E-2</v>
       </c>
       <c r="G15">
-        <f>(F15/E15)*100</f>
+        <f t="shared" si="3"/>
         <v>20.660614266958774</v>
       </c>
     </row>
@@ -5005,4 +5370,1479 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA847CA9-EEAD-47D8-8246-BC1669A39E04}">
+  <dimension ref="D1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4">
+        <v>2531.0100000000002</v>
+      </c>
+      <c r="G4">
+        <f>Tabla6[[#This Row],[T (s)]]/Tabla6[[#This Row],[T (s)]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>236.42</v>
+      </c>
+      <c r="G5">
+        <f>F4/Tabla6[[#This Row],[T (s)]]</f>
+        <v>10.705566364943746</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>77.1447</v>
+      </c>
+      <c r="G6">
+        <f>F4/Tabla6[[#This Row],[T (s)]]</f>
+        <v>32.808605127766398</v>
+      </c>
+    </row>
+    <row r="7" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>847.87</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>82.703999999999994</v>
+      </c>
+      <c r="G8">
+        <f>F7/Tabla6[[#This Row],[T (s)]]</f>
+        <v>10.251862062294448</v>
+      </c>
+    </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>23.554400000000001</v>
+      </c>
+      <c r="G9">
+        <f>F7/Tabla6[[#This Row],[T (s)]]</f>
+        <v>35.996246985701184</v>
+      </c>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>2692.79</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>264.40199999999999</v>
+      </c>
+      <c r="G11">
+        <f>F10/Tabla6[[#This Row],[T (s)]]</f>
+        <v>10.184453975385965</v>
+      </c>
+    </row>
+    <row r="12" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12">
+        <v>86.291600000000003</v>
+      </c>
+      <c r="G12">
+        <f>F10/Tabla6[[#This Row],[T (s)]]</f>
+        <v>31.205702524927105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61388887-C6C4-4F6F-8AD6-C9DE40C79BFF}">
+  <dimension ref="B1:R68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4">
+        <v>18.841999999999999</v>
+      </c>
+      <c r="E4">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>94.21</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4">
+        <v>18.84</v>
+      </c>
+      <c r="J4" s="14">
+        <v>94.21</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="14">
+        <v>33.409999999999997</v>
+      </c>
+      <c r="M4" s="14">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="14">
+        <v>246.38</v>
+      </c>
+      <c r="P4" s="14">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+      <c r="D5">
+        <v>19.164300000000001</v>
+      </c>
+      <c r="E5">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>47.91075</v>
+      </c>
+      <c r="H5">
+        <v>400</v>
+      </c>
+      <c r="I5">
+        <v>19.16</v>
+      </c>
+      <c r="J5" s="14">
+        <v>47.91</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="14">
+        <v>38.56</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="O5" s="14">
+        <v>291.95</v>
+      </c>
+      <c r="P5" s="14">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>17.084399999999999</v>
+      </c>
+      <c r="E6">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>17.084399999999999</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="J6" s="14">
+        <v>17.084</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="14">
+        <v>43.4</v>
+      </c>
+      <c r="M6" s="14">
+        <v>0.434</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="14">
+        <v>335.23</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+      <c r="D7">
+        <v>17.097100000000001</v>
+      </c>
+      <c r="E7">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>8.5485500000000005</v>
+      </c>
+      <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7">
+        <v>17.09</v>
+      </c>
+      <c r="J7" s="14">
+        <v>8.548</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="14">
+        <v>68.540000000000006</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="14">
+        <v>379.27</v>
+      </c>
+      <c r="P7" s="14">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="D8">
+        <v>17.201499999999999</v>
+      </c>
+      <c r="E8">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>4.3003749999999998</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>17.2</v>
+      </c>
+      <c r="J8" s="14">
+        <v>4.3003</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="14">
+        <v>89.16</v>
+      </c>
+      <c r="M8" s="14">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="14">
+        <v>423.52</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>17.438700000000001</v>
+      </c>
+      <c r="E9">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>1.74387</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9">
+        <v>17.43</v>
+      </c>
+      <c r="J9" s="14">
+        <v>1.7430000000000001</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="14">
+        <v>115.64</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="14">
+        <v>469.07</v>
+      </c>
+      <c r="P9" s="14">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>20000</v>
+      </c>
+      <c r="D10">
+        <v>22.3018</v>
+      </c>
+      <c r="E10">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>1.1150899999999999</v>
+      </c>
+      <c r="H10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10">
+        <v>22.3</v>
+      </c>
+      <c r="J10" s="14">
+        <v>1.115</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="14">
+        <v>141.37</v>
+      </c>
+      <c r="M10" s="14">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="14">
+        <v>702.06</v>
+      </c>
+      <c r="P10" s="14">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>30000</v>
+      </c>
+      <c r="D11">
+        <v>23.580500000000001</v>
+      </c>
+      <c r="E11">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.7860166666666667</v>
+      </c>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11">
+        <v>23.58</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="14">
+        <v>173.56</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0.495</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="14">
+        <v>927.77</v>
+      </c>
+      <c r="P11" s="15">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>40000</v>
+      </c>
+      <c r="D12">
+        <v>28.273800000000001</v>
+      </c>
+      <c r="E12">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.70684499999999995</v>
+      </c>
+      <c r="H12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12">
+        <v>28.27</v>
+      </c>
+      <c r="J12">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="K12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>195.79</v>
+      </c>
+      <c r="M12">
+        <v>0.48899999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>60000</v>
+      </c>
+      <c r="D13">
+        <v>33.410499999999999</v>
+      </c>
+      <c r="E13">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.55684166666666657</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>80000</v>
+      </c>
+      <c r="D14">
+        <v>38.565800000000003</v>
+      </c>
+      <c r="E14">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48207250000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>100000</v>
+      </c>
+      <c r="D15">
+        <v>43.403700000000001</v>
+      </c>
+      <c r="E15">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.43403700000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>150000</v>
+      </c>
+      <c r="D16">
+        <v>68.543400000000005</v>
+      </c>
+      <c r="E16">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.45695600000000008</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>200000</v>
+      </c>
+      <c r="D17">
+        <v>89.162099999999995</v>
+      </c>
+      <c r="E17">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.4458105</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>250000</v>
+      </c>
+      <c r="D18">
+        <v>115.643</v>
+      </c>
+      <c r="E18">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46257200000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>300000</v>
+      </c>
+      <c r="D19">
+        <v>141.374</v>
+      </c>
+      <c r="E19">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.4712466666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>350000</v>
+      </c>
+      <c r="D20">
+        <v>173.56299999999999</v>
+      </c>
+      <c r="E20">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.49589428571428568</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>400000</v>
+      </c>
+      <c r="D21">
+        <v>195.79300000000001</v>
+      </c>
+      <c r="E21">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48948250000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>500000</v>
+      </c>
+      <c r="D22">
+        <v>246.38900000000001</v>
+      </c>
+      <c r="E22">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.49277800000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>600000</v>
+      </c>
+      <c r="D23">
+        <v>291.95100000000002</v>
+      </c>
+      <c r="E23">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48658500000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>700000</v>
+      </c>
+      <c r="D24">
+        <v>335.23500000000001</v>
+      </c>
+      <c r="E24">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.47890714285714286</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>800000</v>
+      </c>
+      <c r="D25">
+        <v>379.27300000000002</v>
+      </c>
+      <c r="E25">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.47409125000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>900000</v>
+      </c>
+      <c r="D26">
+        <v>423.52100000000002</v>
+      </c>
+      <c r="E26">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.47057888888888888</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>1000000</v>
+      </c>
+      <c r="D27">
+        <v>469.07100000000003</v>
+      </c>
+      <c r="E27">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46907100000000007</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>1500000</v>
+      </c>
+      <c r="D28">
+        <v>702.06799999999998</v>
+      </c>
+      <c r="E28">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46804533333333331</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>2000000</v>
+      </c>
+      <c r="D29">
+        <v>927.77499999999998</v>
+      </c>
+      <c r="E29">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46388749999999995</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>200</v>
+      </c>
+      <c r="D30">
+        <v>4.2511799999999997</v>
+      </c>
+      <c r="E30">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>21.255899999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>400</v>
+      </c>
+      <c r="D31">
+        <v>4.3825000000000003</v>
+      </c>
+      <c r="E31">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>10.956250000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1000</v>
+      </c>
+      <c r="D32">
+        <v>4.4242800000000004</v>
+      </c>
+      <c r="E32">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>4.4242800000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>2000</v>
+      </c>
+      <c r="D33">
+        <v>4.4725599999999996</v>
+      </c>
+      <c r="E33">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>2.2362799999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>4000</v>
+      </c>
+      <c r="D34">
+        <v>4.5078199999999997</v>
+      </c>
+      <c r="E34">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>1.1269549999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>10000</v>
+      </c>
+      <c r="D35">
+        <v>4.64262</v>
+      </c>
+      <c r="E35">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46426200000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>20000</v>
+      </c>
+      <c r="D36">
+        <v>6.0775300000000003</v>
+      </c>
+      <c r="E36">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.30387650000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>20000</v>
+      </c>
+      <c r="D37">
+        <v>6.1955400000000003</v>
+      </c>
+      <c r="E37">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.30977700000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>30000</v>
+      </c>
+      <c r="D38">
+        <v>6.4583899999999996</v>
+      </c>
+      <c r="E38">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.21527966666666667</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>40000</v>
+      </c>
+      <c r="D39">
+        <v>7.6532600000000004</v>
+      </c>
+      <c r="E39">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.19133150000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>60000</v>
+      </c>
+      <c r="D40">
+        <v>9.4447200000000002</v>
+      </c>
+      <c r="E40">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.157412</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>80000</v>
+      </c>
+      <c r="D41">
+        <v>10.9232</v>
+      </c>
+      <c r="E41">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.13653999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>100000</v>
+      </c>
+      <c r="D42">
+        <v>13.191000000000001</v>
+      </c>
+      <c r="E42">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.13191</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>150000</v>
+      </c>
+      <c r="D43">
+        <v>23.0747</v>
+      </c>
+      <c r="E43">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.15383133333333335</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>200000</v>
+      </c>
+      <c r="D44">
+        <v>30.912700000000001</v>
+      </c>
+      <c r="E44">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.15456350000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>250000</v>
+      </c>
+      <c r="D45">
+        <v>41.323999999999998</v>
+      </c>
+      <c r="E45">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.165296</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>350000</v>
+      </c>
+      <c r="D46">
+        <v>58.703600000000002</v>
+      </c>
+      <c r="E46">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.16772457142857145</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>400000</v>
+      </c>
+      <c r="D47">
+        <v>64.938500000000005</v>
+      </c>
+      <c r="E47">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.16234625</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>1500000</v>
+      </c>
+      <c r="D48">
+        <v>227.02</v>
+      </c>
+      <c r="E48">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.15134666666666668</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>2000000</v>
+      </c>
+      <c r="D49">
+        <v>299.822</v>
+      </c>
+      <c r="E49">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.14991099999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>200</v>
+      </c>
+      <c r="D50">
+        <v>14.4727</v>
+      </c>
+      <c r="E50">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>72.363500000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51">
+        <v>400</v>
+      </c>
+      <c r="D51">
+        <v>14.583500000000001</v>
+      </c>
+      <c r="E51">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>36.458750000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>1000</v>
+      </c>
+      <c r="D52">
+        <v>13.609400000000001</v>
+      </c>
+      <c r="E52">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>13.609400000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>2000</v>
+      </c>
+      <c r="D53">
+        <v>13.638</v>
+      </c>
+      <c r="E53">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>6.819</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>4000</v>
+      </c>
+      <c r="D54">
+        <v>13.8041</v>
+      </c>
+      <c r="E54">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>3.451025</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>10000</v>
+      </c>
+      <c r="D55">
+        <v>14.319800000000001</v>
+      </c>
+      <c r="E55">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>1.43198</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>20000</v>
+      </c>
+      <c r="D56">
+        <v>18.740500000000001</v>
+      </c>
+      <c r="E56">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.93702500000000011</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>30000</v>
+      </c>
+      <c r="D57">
+        <v>19.7819</v>
+      </c>
+      <c r="E57">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.65939666666666663</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>40000</v>
+      </c>
+      <c r="D58">
+        <v>23.7239</v>
+      </c>
+      <c r="E58">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.59309749999999994</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>60000</v>
+      </c>
+      <c r="D59">
+        <v>29.398900000000001</v>
+      </c>
+      <c r="E59">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48998166666666665</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>80000</v>
+      </c>
+      <c r="D60">
+        <v>37.430100000000003</v>
+      </c>
+      <c r="E60">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.46787625000000005</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>100000</v>
+      </c>
+      <c r="D61">
+        <v>51.010599999999997</v>
+      </c>
+      <c r="E61">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.51010599999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>150000</v>
+      </c>
+      <c r="D62">
+        <v>80.215500000000006</v>
+      </c>
+      <c r="E62">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.53477000000000008</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>200000</v>
+      </c>
+      <c r="D63">
+        <v>104.756</v>
+      </c>
+      <c r="E63">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.52377999999999991</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>250000</v>
+      </c>
+      <c r="D64">
+        <v>135.49299999999999</v>
+      </c>
+      <c r="E64">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.5419719999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>350000</v>
+      </c>
+      <c r="D65">
+        <v>188.30500000000001</v>
+      </c>
+      <c r="E65">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.53801428571428578</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>400000</v>
+      </c>
+      <c r="D66">
+        <v>208.50399999999999</v>
+      </c>
+      <c r="E66">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.52125999999999995</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>1500000</v>
+      </c>
+      <c r="D67">
+        <v>728.73500000000001</v>
+      </c>
+      <c r="E67">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48582333333333333</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>2000000</v>
+      </c>
+      <c r="D68">
+        <v>962.81100000000004</v>
+      </c>
+      <c r="E68">
+        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
+        <v>0.48140550000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Memoria/library/mediciones auxiliares.xlsx
+++ b/Memoria/library/mediciones auxiliares.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\TFG\Memoria\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80340FEC-BBD7-433B-9D96-6C5373411089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8051A271-1D7B-4904-AC3B-F76DDEC9EAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Euler" sheetId="3" r:id="rId1"/>
     <sheet name="OMP-Br1d" sheetId="1" r:id="rId2"/>
     <sheet name="OMP-Br2d" sheetId="2" r:id="rId3"/>
     <sheet name="CUDA-Br2d" sheetId="4" r:id="rId4"/>
-    <sheet name="CUDA-tams" sheetId="5" r:id="rId5"/>
+    <sheet name="CUDA-RK-Br1d" sheetId="5" r:id="rId5"/>
+    <sheet name="Graph" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="66">
   <si>
     <t>Runge Kutta</t>
   </si>
@@ -227,12 +228,24 @@
   <si>
     <t>10K</t>
   </si>
+  <si>
+    <t>CUDA ABM Brusselator2D, varios tamaños, comparamos con y sin graph</t>
+  </si>
+  <si>
+    <t>T - CON</t>
+  </si>
+  <si>
+    <t>T - SIN</t>
+  </si>
+  <si>
+    <t>Sin/Con</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,8 +272,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +290,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -356,7 +381,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -370,16 +395,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{894E2A58-4AB2-4DD0-992A-D8EFC287A90D}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F071A7C7-C907-4782-97BC-1691119DD71E}"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="32">
     <dxf>
       <font>
         <b val="0"/>
@@ -990,6 +1014,9 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3725,8 +3752,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}" name="Tabla7" displayName="Tabla7" ref="B3:E68" totalsRowShown="0">
-  <autoFilter ref="B3:E68" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}" name="Tabla7" displayName="Tabla7" ref="B3:E29" totalsRowShown="0">
+  <autoFilter ref="B3:E29" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{644F7757-56D6-4333-9A04-BB025A3FA537}" name="Solver"/>
     <tableColumn id="9" xr3:uid="{7A4B951A-072B-4FA9-BB96-812FB6E68533}" name="neqn"/>
@@ -3740,18 +3767,32 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="H3:P12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{932C3C52-A732-48FA-B5C5-2E96D1AF7393}" name="neqn"/>
     <tableColumn id="2" xr3:uid="{180E0420-BB3F-4A15-AA9C-8504B61074B7}" name="T (s)"/>
-    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}" name="Tabla9" displayName="Tabla9" ref="C3:E18" totalsRowShown="0">
+  <autoFilter ref="C3:E18" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}"/>
+  <tableColumns count="3">
+    <tableColumn id="10" xr3:uid="{386D6B24-9F12-4906-A98F-C1ECE9B2AF91}" name="T - CON"/>
+    <tableColumn id="12" xr3:uid="{BF967619-27A5-4370-8EB3-0CF9D0A5FB92}" name="T - SIN"/>
+    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="31">
+      <calculatedColumnFormula>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5546,7 +5587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61388887-C6C4-4F6F-8AD6-C9DE40C79BFF}">
-  <dimension ref="B1:R68"/>
+  <dimension ref="B1:R29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
@@ -5560,15 +5601,15 @@
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -5589,7 +5630,7 @@
       <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" t="s">
         <v>30</v>
       </c>
       <c r="K3" t="s">
@@ -5598,7 +5639,7 @@
       <c r="L3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" t="s">
         <v>33</v>
       </c>
       <c r="N3" t="s">
@@ -5607,11 +5648,9 @@
       <c r="O3" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -5633,29 +5672,27 @@
       <c r="I4">
         <v>18.84</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4">
         <v>94.21</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4">
         <v>33.409999999999997</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4">
         <v>0.55600000000000005</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4">
         <v>246.38</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4">
         <v>0.49199999999999999</v>
       </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -5677,29 +5714,27 @@
       <c r="I5">
         <v>19.16</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5">
         <v>47.91</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5">
         <v>38.56</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5">
         <v>0.48199999999999998</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5">
         <v>291.95</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5">
         <v>0.48599999999999999</v>
       </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -5721,29 +5756,27 @@
       <c r="I6">
         <v>17.079999999999998</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6">
         <v>17.084</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6">
         <v>43.4</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6">
         <v>0.434</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6">
         <v>335.23</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6">
         <v>0.47799999999999998</v>
       </c>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -5765,29 +5798,27 @@
       <c r="I7">
         <v>17.09</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7">
         <v>8.548</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7">
         <v>68.540000000000006</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7">
         <v>0.45600000000000002</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7">
         <v>379.27</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7">
         <v>0.47399999999999998</v>
       </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -5809,29 +5840,27 @@
       <c r="I8">
         <v>17.2</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8">
         <v>4.3003</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8">
         <v>89.16</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N8" s="14" t="s">
+      <c r="N8" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8">
         <v>423.52</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8">
         <v>0.47</v>
       </c>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -5853,29 +5882,27 @@
       <c r="I9">
         <v>17.43</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9">
         <v>1.7430000000000001</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" t="s">
         <v>48</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9">
         <v>115.64</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9">
         <v>0.46200000000000002</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9">
         <v>469.07</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9">
         <v>0.46899999999999997</v>
       </c>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -5897,29 +5924,27 @@
       <c r="I10">
         <v>22.3</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10">
         <v>1.115</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10">
         <v>141.37</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10">
         <v>0.47099999999999997</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" t="s">
         <v>58</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10">
         <v>702.06</v>
       </c>
-      <c r="P10" s="14">
+      <c r="P10">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -5941,29 +5966,27 @@
       <c r="I11">
         <v>23.58</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11">
         <v>0.78600000000000003</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11">
         <v>173.56</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11">
         <v>0.495</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" t="s">
         <v>59</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11">
         <v>927.77</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11">
         <v>0.46300000000000002</v>
       </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -6251,591 +6274,6 @@
       <c r="E29">
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.46388749999999995</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30">
-        <v>200</v>
-      </c>
-      <c r="D30">
-        <v>4.2511799999999997</v>
-      </c>
-      <c r="E30">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>21.255899999999997</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>400</v>
-      </c>
-      <c r="D31">
-        <v>4.3825000000000003</v>
-      </c>
-      <c r="E31">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>10.956250000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32">
-        <v>1000</v>
-      </c>
-      <c r="D32">
-        <v>4.4242800000000004</v>
-      </c>
-      <c r="E32">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>4.4242800000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33">
-        <v>2000</v>
-      </c>
-      <c r="D33">
-        <v>4.4725599999999996</v>
-      </c>
-      <c r="E33">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>2.2362799999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34">
-        <v>4000</v>
-      </c>
-      <c r="D34">
-        <v>4.5078199999999997</v>
-      </c>
-      <c r="E34">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>1.1269549999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35">
-        <v>10000</v>
-      </c>
-      <c r="D35">
-        <v>4.64262</v>
-      </c>
-      <c r="E35">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.46426200000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36">
-        <v>20000</v>
-      </c>
-      <c r="D36">
-        <v>6.0775300000000003</v>
-      </c>
-      <c r="E36">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.30387650000000005</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37">
-        <v>20000</v>
-      </c>
-      <c r="D37">
-        <v>6.1955400000000003</v>
-      </c>
-      <c r="E37">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.30977700000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38">
-        <v>30000</v>
-      </c>
-      <c r="D38">
-        <v>6.4583899999999996</v>
-      </c>
-      <c r="E38">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.21527966666666667</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39">
-        <v>40000</v>
-      </c>
-      <c r="D39">
-        <v>7.6532600000000004</v>
-      </c>
-      <c r="E39">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.19133150000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40">
-        <v>60000</v>
-      </c>
-      <c r="D40">
-        <v>9.4447200000000002</v>
-      </c>
-      <c r="E40">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.157412</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41">
-        <v>80000</v>
-      </c>
-      <c r="D41">
-        <v>10.9232</v>
-      </c>
-      <c r="E41">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.13653999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42">
-        <v>100000</v>
-      </c>
-      <c r="D42">
-        <v>13.191000000000001</v>
-      </c>
-      <c r="E42">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.13191</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43">
-        <v>150000</v>
-      </c>
-      <c r="D43">
-        <v>23.0747</v>
-      </c>
-      <c r="E43">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.15383133333333335</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44">
-        <v>200000</v>
-      </c>
-      <c r="D44">
-        <v>30.912700000000001</v>
-      </c>
-      <c r="E44">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.15456350000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45">
-        <v>250000</v>
-      </c>
-      <c r="D45">
-        <v>41.323999999999998</v>
-      </c>
-      <c r="E45">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.165296</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46">
-        <v>350000</v>
-      </c>
-      <c r="D46">
-        <v>58.703600000000002</v>
-      </c>
-      <c r="E46">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.16772457142857145</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47">
-        <v>400000</v>
-      </c>
-      <c r="D47">
-        <v>64.938500000000005</v>
-      </c>
-      <c r="E47">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.16234625</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48">
-        <v>1500000</v>
-      </c>
-      <c r="D48">
-        <v>227.02</v>
-      </c>
-      <c r="E48">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.15134666666666668</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49">
-        <v>2000000</v>
-      </c>
-      <c r="D49">
-        <v>299.822</v>
-      </c>
-      <c r="E49">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.14991099999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50">
-        <v>200</v>
-      </c>
-      <c r="D50">
-        <v>14.4727</v>
-      </c>
-      <c r="E50">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>72.363500000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51">
-        <v>400</v>
-      </c>
-      <c r="D51">
-        <v>14.583500000000001</v>
-      </c>
-      <c r="E51">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>36.458750000000002</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52">
-        <v>1000</v>
-      </c>
-      <c r="D52">
-        <v>13.609400000000001</v>
-      </c>
-      <c r="E52">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>13.609400000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53">
-        <v>2000</v>
-      </c>
-      <c r="D53">
-        <v>13.638</v>
-      </c>
-      <c r="E53">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>6.819</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54">
-        <v>4000</v>
-      </c>
-      <c r="D54">
-        <v>13.8041</v>
-      </c>
-      <c r="E54">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>3.451025</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55">
-        <v>10000</v>
-      </c>
-      <c r="D55">
-        <v>14.319800000000001</v>
-      </c>
-      <c r="E55">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>1.43198</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56">
-        <v>20000</v>
-      </c>
-      <c r="D56">
-        <v>18.740500000000001</v>
-      </c>
-      <c r="E56">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.93702500000000011</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57">
-        <v>30000</v>
-      </c>
-      <c r="D57">
-        <v>19.7819</v>
-      </c>
-      <c r="E57">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.65939666666666663</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58">
-        <v>40000</v>
-      </c>
-      <c r="D58">
-        <v>23.7239</v>
-      </c>
-      <c r="E58">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.59309749999999994</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59">
-        <v>60000</v>
-      </c>
-      <c r="D59">
-        <v>29.398900000000001</v>
-      </c>
-      <c r="E59">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.48998166666666665</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60">
-        <v>80000</v>
-      </c>
-      <c r="D60">
-        <v>37.430100000000003</v>
-      </c>
-      <c r="E60">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.46787625000000005</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61">
-        <v>100000</v>
-      </c>
-      <c r="D61">
-        <v>51.010599999999997</v>
-      </c>
-      <c r="E61">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.51010599999999995</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62">
-        <v>150000</v>
-      </c>
-      <c r="D62">
-        <v>80.215500000000006</v>
-      </c>
-      <c r="E62">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.53477000000000008</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63">
-        <v>200000</v>
-      </c>
-      <c r="D63">
-        <v>104.756</v>
-      </c>
-      <c r="E63">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.52377999999999991</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64">
-        <v>250000</v>
-      </c>
-      <c r="D64">
-        <v>135.49299999999999</v>
-      </c>
-      <c r="E64">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.5419719999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65">
-        <v>350000</v>
-      </c>
-      <c r="D65">
-        <v>188.30500000000001</v>
-      </c>
-      <c r="E65">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.53801428571428578</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66">
-        <v>400000</v>
-      </c>
-      <c r="D66">
-        <v>208.50399999999999</v>
-      </c>
-      <c r="E66">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.52125999999999995</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67">
-        <v>1500000</v>
-      </c>
-      <c r="D67">
-        <v>728.73500000000001</v>
-      </c>
-      <c r="E67">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.48582333333333333</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68">
-        <v>2000000</v>
-      </c>
-      <c r="D68">
-        <v>962.81100000000004</v>
-      </c>
-      <c r="E68">
-        <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
-        <v>0.48140550000000004</v>
       </c>
     </row>
   </sheetData>
@@ -6845,4 +6283,267 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B2D2FD-67A7-474C-A0C8-ADED995BDF7A}">
+  <dimension ref="B1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>1250</v>
+      </c>
+      <c r="C4">
+        <v>15.6045</v>
+      </c>
+      <c r="D4">
+        <v>15.772399999999999</v>
+      </c>
+      <c r="E4">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>1.0107597167483737</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
+        <v>5000</v>
+      </c>
+      <c r="C5">
+        <v>15.341100000000001</v>
+      </c>
+      <c r="D5">
+        <v>15.7544</v>
+      </c>
+      <c r="E5">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>1.0269407017749705</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>11250</v>
+      </c>
+      <c r="C6">
+        <v>15.9351</v>
+      </c>
+      <c r="D6">
+        <v>16.156099999999999</v>
+      </c>
+      <c r="E6">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>1.0138687551380285</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C7">
+        <v>22.657800000000002</v>
+      </c>
+      <c r="D7">
+        <v>22.6586</v>
+      </c>
+      <c r="E7">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>1.0000353079292781</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>31250</v>
+      </c>
+      <c r="C8">
+        <v>23.816099999999999</v>
+      </c>
+      <c r="D8">
+        <v>23.604900000000001</v>
+      </c>
+      <c r="E8">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.99113204932797572</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
+        <v>45000</v>
+      </c>
+      <c r="C9">
+        <v>31.638100000000001</v>
+      </c>
+      <c r="D9">
+        <v>30.777699999999999</v>
+      </c>
+      <c r="E9">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.97280494087824487</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>61250</v>
+      </c>
+      <c r="C10">
+        <v>39.993499999999997</v>
+      </c>
+      <c r="D10">
+        <v>39.1357</v>
+      </c>
+      <c r="E10">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.978551514621126</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
+        <v>80000</v>
+      </c>
+      <c r="C11">
+        <v>47.031500000000001</v>
+      </c>
+      <c r="D11">
+        <v>43.573999999999998</v>
+      </c>
+      <c r="E11">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.92648544060895355</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>101250</v>
+      </c>
+      <c r="C12">
+        <v>69.774000000000001</v>
+      </c>
+      <c r="D12">
+        <v>62.0139</v>
+      </c>
+      <c r="E12">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.88878235445868081</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
+        <v>125000</v>
+      </c>
+      <c r="C13">
+        <v>99.3</v>
+      </c>
+      <c r="D13">
+        <v>86.291600000000003</v>
+      </c>
+      <c r="E13">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.86899899295065464</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="2">
+        <v>180000</v>
+      </c>
+      <c r="C14">
+        <v>147.21700000000001</v>
+      </c>
+      <c r="D14">
+        <v>120.547</v>
+      </c>
+      <c r="E14">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.81883885692549085</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
+        <v>320000</v>
+      </c>
+      <c r="C15">
+        <v>264.62400000000002</v>
+      </c>
+      <c r="D15">
+        <v>213.41800000000001</v>
+      </c>
+      <c r="E15">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.80649525364290464</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="2">
+        <v>500000</v>
+      </c>
+      <c r="C16">
+        <v>392.97199999999998</v>
+      </c>
+      <c r="D16">
+        <v>313.98399999999998</v>
+      </c>
+      <c r="E16">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.79899840192176541</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
+        <v>720000</v>
+      </c>
+      <c r="C17">
+        <v>573.024</v>
+      </c>
+      <c r="D17">
+        <v>458.03</v>
+      </c>
+      <c r="E17">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.79932079633662811</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>980000</v>
+      </c>
+      <c r="C18">
+        <v>772.95399999999995</v>
+      </c>
+      <c r="D18">
+        <v>615.16499999999996</v>
+      </c>
+      <c r="E18">
+        <f>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</f>
+        <v>0.79586236697138513</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Memoria/library/mediciones auxiliares.xlsx
+++ b/Memoria/library/mediciones auxiliares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\TFG\Memoria\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8051A271-1D7B-4904-AC3B-F76DDEC9EAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60552AEB-2B91-4A02-BCF4-54C1E2C1E491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Euler" sheetId="3" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="CUDA-Br2d" sheetId="4" r:id="rId4"/>
     <sheet name="CUDA-RK-Br1d" sheetId="5" r:id="rId5"/>
     <sheet name="Graph" sheetId="6" r:id="rId6"/>
+    <sheet name="ShuffleGrid" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="75">
   <si>
     <t>Runge Kutta</t>
   </si>
@@ -240,6 +241,33 @@
   <si>
     <t>Sin/Con</t>
   </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Comparativa por tamaños de ejecución CUDA AB4 Brusselator1D estándar, shuffle, y grid multidimensional</t>
+  </si>
+  <si>
+    <t>Estándar</t>
+  </si>
+  <si>
+    <t>Grid</t>
+  </si>
+  <si>
+    <t>Shuffle</t>
+  </si>
+  <si>
+    <t>Estandar</t>
+  </si>
+  <si>
+    <t>Estandar2</t>
+  </si>
+  <si>
+    <t>Shuffle2</t>
+  </si>
+  <si>
+    <t>Grid2</t>
+  </si>
 </sst>
 </file>
 
@@ -404,198 +432,6 @@
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F071A7C7-C907-4782-97BC-1691119DD71E}"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1017,6 +853,198 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3651,7 +3679,7 @@
     <tableColumn id="7" xr3:uid="{64FA0956-3E24-4150-B966-D174B7BC073B}" name="Hebras"/>
     <tableColumn id="10" xr3:uid="{1B8321A3-89E7-440F-AC38-60832AF9D3BF}" name="T (s)"/>
     <tableColumn id="4" xr3:uid="{2A319FA1-3453-4EE4-B2DC-4F5247C2B6CA}" name="Speedup"/>
-    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="30">
+    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="22">
       <calculatedColumnFormula>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3659,19 +3687,72 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}" name="Tabla10" displayName="Tabla10" ref="B4:D88" totalsRowShown="0">
+  <autoFilter ref="B4:D88" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}"/>
+  <tableColumns count="3">
+    <tableColumn id="4" xr3:uid="{F8B9704B-26A7-4AA4-BF1B-2251CDAA311E}" name="Tipo"/>
+    <tableColumn id="9" xr3:uid="{19ABDBC2-83A4-4900-A721-22EA32EE82C4}" name="neqn"/>
+    <tableColumn id="10" xr3:uid="{F19E0A1E-C76F-49BE-B442-9BCB56454C3E}" name="T (s)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}" name="Tabla11" displayName="Tabla11" ref="J4:L31" totalsRowShown="0">
+  <autoFilter ref="J4:L31" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}"/>
+  <tableColumns count="3">
+    <tableColumn id="4" xr3:uid="{D59140D9-2F79-4E66-950E-9DC22FE56F4F}" name="Tipo"/>
+    <tableColumn id="9" xr3:uid="{94D77E23-F420-4A67-84D7-B9DFA1FCD3D8}" name="neqn"/>
+    <tableColumn id="10" xr3:uid="{72281BD8-0B0E-4D17-AC0B-998CFD8F64DA}" name="T (s)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}" name="Tabla12" displayName="Tabla12" ref="F4:H31" totalsRowShown="0">
+  <autoFilter ref="F4:H31" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}"/>
+  <tableColumns count="3">
+    <tableColumn id="4" xr3:uid="{5FCE846A-A473-4B63-819C-01059D663651}" name="Nombre"/>
+    <tableColumn id="9" xr3:uid="{6DF642FA-F63C-43D5-82B9-6601800B4249}" name="neqn"/>
+    <tableColumn id="10" xr3:uid="{66FB404C-4698-4C2C-BBD1-BD404E0ED128}" name="T (s)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}" name="Tabla13" displayName="Tabla13" ref="O4:V17" totalsRowShown="0">
+  <autoFilter ref="O4:V17" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{CE9A48D7-9420-4A5D-BEE4-7937AE189F35}" name="neqn"/>
+    <tableColumn id="2" xr3:uid="{A20E631F-56F2-48B7-89B6-A897472E998A}" name="Estandar"/>
+    <tableColumn id="3" xr3:uid="{C4A2CE58-564C-4CCF-AC38-403D8F981435}" name="Shuffle"/>
+    <tableColumn id="4" xr3:uid="{B73985C0-8575-44BA-9B96-8D350FF00DB0}" name="Grid"/>
+    <tableColumn id="5" xr3:uid="{96D98994-B64F-4F12-A7C1-9115F1D73C3D}" name="neqn2"/>
+    <tableColumn id="6" xr3:uid="{81A7D7F1-86B9-477E-B700-6BCDE6B91A88}" name="Estandar2"/>
+    <tableColumn id="7" xr3:uid="{C5DAE265-3243-45D3-90A6-003BF917C986}" name="Shuffle2"/>
+    <tableColumn id="8" xr3:uid="{AFE4D93B-9CAB-4B03-98CB-2F005CA7A352}" name="Grid2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="21">
   <autoFilter ref="A17:F23" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:D23">
     <sortCondition descending="1" ref="D17:D23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="17"/>
     <tableColumn id="5" xr3:uid="{BF613CE6-6DEF-4C0B-848D-8F065FCF2C50}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="16">
       <calculatedColumnFormula>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3680,18 +3761,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="15">
   <autoFilter ref="A9:F15" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:D15">
     <sortCondition descending="1" ref="D9:D15"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="11"/>
     <tableColumn id="5" xr3:uid="{417AEB65-89EB-4AD8-BE23-D32970ABEDB3}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="18">
+    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="10">
       <calculatedColumnFormula>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3711,7 +3792,7 @@
     <tableColumn id="3" xr3:uid="{3A3C5E88-C7DA-483A-917E-BB271E1A560D}" name="Tipo"/>
     <tableColumn id="10" xr3:uid="{16A7936E-BB2A-4361-A80F-5CD098124D72}" name="T (s)"/>
     <tableColumn id="1" xr3:uid="{99669171-F1C7-4284-B05F-40B0C07B15FF}" name="Speedup"/>
-    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="17">
+    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="9">
       <calculatedColumnFormula>Tabla2[[#This Row],[Speedup]]/Tabla2[[#This Row],[Hebras]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3720,14 +3801,14 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="K3:O12" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="1">
       <calculatedColumnFormula>Tabla3[[#This Row],[Speedup]]/Tabla3[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3758,7 +3839,7 @@
     <tableColumn id="1" xr3:uid="{644F7757-56D6-4333-9A04-BB025A3FA537}" name="Solver"/>
     <tableColumn id="9" xr3:uid="{7A4B951A-072B-4FA9-BB96-812FB6E68533}" name="neqn"/>
     <tableColumn id="10" xr3:uid="{27844286-B464-4C11-8051-BCFF52593894}" name="T (s)"/>
-    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="31">
       <calculatedColumnFormula>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3767,18 +3848,18 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="30">
   <autoFilter ref="H3:P12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{932C3C52-A732-48FA-B5C5-2E96D1AF7393}" name="neqn"/>
     <tableColumn id="2" xr3:uid="{180E0420-BB3F-4A15-AA9C-8504B61074B7}" name="T (s)"/>
-    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3790,7 +3871,7 @@
   <tableColumns count="3">
     <tableColumn id="10" xr3:uid="{386D6B24-9F12-4906-A98F-C1ECE9B2AF91}" name="T - CON"/>
     <tableColumn id="12" xr3:uid="{BF967619-27A5-4370-8EB3-0CF9D0A5FB92}" name="T - SIN"/>
-    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="31">
+    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="0">
       <calculatedColumnFormula>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6546,4 +6627,1811 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2834D68-C9F2-4F19-B00C-81124B4CC62E}">
+  <dimension ref="B1:V88"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
+        <v>72</v>
+      </c>
+      <c r="U4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>200</v>
+      </c>
+      <c r="D5">
+        <v>4.2511799999999997</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
+      <c r="H5">
+        <v>4.2739500000000001</v>
+      </c>
+      <c r="J5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5">
+        <v>200</v>
+      </c>
+      <c r="L5">
+        <v>4.4091699999999996</v>
+      </c>
+      <c r="O5">
+        <v>200</v>
+      </c>
+      <c r="P5">
+        <v>4.2511799999999997</v>
+      </c>
+      <c r="Q5">
+        <v>4.2739500000000001</v>
+      </c>
+      <c r="R5">
+        <v>4.4091699999999996</v>
+      </c>
+      <c r="S5">
+        <v>300000</v>
+      </c>
+      <c r="T5">
+        <v>49.077300000000001</v>
+      </c>
+      <c r="U5">
+        <v>47.618600000000001</v>
+      </c>
+      <c r="V5">
+        <v>47.109400000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6">
+        <v>400</v>
+      </c>
+      <c r="D6">
+        <v>4.3825000000000003</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6">
+        <v>400</v>
+      </c>
+      <c r="H6">
+        <v>4.4763099999999998</v>
+      </c>
+      <c r="J6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6">
+        <v>400</v>
+      </c>
+      <c r="L6">
+        <v>4.4284499999999998</v>
+      </c>
+      <c r="O6">
+        <v>400</v>
+      </c>
+      <c r="P6">
+        <v>4.3825000000000003</v>
+      </c>
+      <c r="Q6">
+        <v>4.4763099999999998</v>
+      </c>
+      <c r="R6">
+        <v>4.4284499999999998</v>
+      </c>
+      <c r="S6">
+        <v>400000</v>
+      </c>
+      <c r="T6">
+        <v>64.316400000000002</v>
+      </c>
+      <c r="U6">
+        <v>64.066100000000006</v>
+      </c>
+      <c r="V6">
+        <v>62.265799999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>4.4242800000000004</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>4.4807300000000003</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>4.4563800000000002</v>
+      </c>
+      <c r="O7">
+        <v>1000</v>
+      </c>
+      <c r="P7">
+        <v>4.4242800000000004</v>
+      </c>
+      <c r="Q7">
+        <v>4.4807300000000003</v>
+      </c>
+      <c r="R7">
+        <v>4.4563800000000002</v>
+      </c>
+      <c r="S7">
+        <v>500000</v>
+      </c>
+      <c r="T7">
+        <v>78.499799999999993</v>
+      </c>
+      <c r="U7">
+        <v>79.241900000000001</v>
+      </c>
+      <c r="V7">
+        <v>79.390100000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
+      <c r="D8">
+        <v>4.4725599999999996</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8">
+        <v>2000</v>
+      </c>
+      <c r="H8">
+        <v>4.4973900000000002</v>
+      </c>
+      <c r="J8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8">
+        <v>2000</v>
+      </c>
+      <c r="L8">
+        <v>4.5598000000000001</v>
+      </c>
+      <c r="O8">
+        <v>2000</v>
+      </c>
+      <c r="P8">
+        <v>4.4725599999999996</v>
+      </c>
+      <c r="Q8">
+        <v>4.4973900000000002</v>
+      </c>
+      <c r="R8">
+        <v>4.5598000000000001</v>
+      </c>
+      <c r="S8">
+        <v>600000</v>
+      </c>
+      <c r="T8">
+        <v>92.214299999999994</v>
+      </c>
+      <c r="U8">
+        <v>93.808400000000006</v>
+      </c>
+      <c r="V8">
+        <v>94.276300000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9">
+        <v>4000</v>
+      </c>
+      <c r="D9">
+        <v>4.5078199999999997</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9">
+        <v>4000</v>
+      </c>
+      <c r="H9">
+        <v>4.5514799999999997</v>
+      </c>
+      <c r="J9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>4000</v>
+      </c>
+      <c r="L9">
+        <v>4.5202</v>
+      </c>
+      <c r="O9">
+        <v>4000</v>
+      </c>
+      <c r="P9">
+        <v>4.5078199999999997</v>
+      </c>
+      <c r="Q9">
+        <v>4.5514799999999997</v>
+      </c>
+      <c r="R9">
+        <v>4.5202</v>
+      </c>
+      <c r="S9">
+        <v>700000</v>
+      </c>
+      <c r="T9">
+        <v>108.71599999999999</v>
+      </c>
+      <c r="U9">
+        <v>108.27200000000001</v>
+      </c>
+      <c r="V9">
+        <v>108.879</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+      <c r="D10">
+        <v>4.64262</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>10000</v>
+      </c>
+      <c r="H10">
+        <v>4.7199299999999997</v>
+      </c>
+      <c r="J10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K10">
+        <v>10000</v>
+      </c>
+      <c r="L10">
+        <v>4.6811100000000003</v>
+      </c>
+      <c r="O10">
+        <v>10000</v>
+      </c>
+      <c r="P10">
+        <v>4.64262</v>
+      </c>
+      <c r="Q10">
+        <v>4.7199299999999997</v>
+      </c>
+      <c r="R10">
+        <v>4.6811100000000003</v>
+      </c>
+      <c r="S10">
+        <v>800000</v>
+      </c>
+      <c r="T10">
+        <v>123.306</v>
+      </c>
+      <c r="U10">
+        <v>122.247</v>
+      </c>
+      <c r="V10">
+        <v>122.502</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11">
+        <v>20000</v>
+      </c>
+      <c r="D11">
+        <v>6.0775300000000003</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11">
+        <v>20000</v>
+      </c>
+      <c r="H11">
+        <v>6.194</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11">
+        <v>20000</v>
+      </c>
+      <c r="L11">
+        <v>6.2668900000000001</v>
+      </c>
+      <c r="O11">
+        <v>20000</v>
+      </c>
+      <c r="P11">
+        <v>6.0775300000000003</v>
+      </c>
+      <c r="Q11">
+        <v>6.194</v>
+      </c>
+      <c r="R11">
+        <v>6.2668900000000001</v>
+      </c>
+      <c r="S11">
+        <v>900000</v>
+      </c>
+      <c r="T11">
+        <v>137.59899999999999</v>
+      </c>
+      <c r="U11">
+        <v>136.72999999999999</v>
+      </c>
+      <c r="V11">
+        <v>137.17400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12">
+        <v>30000</v>
+      </c>
+      <c r="D12">
+        <v>6.4583899999999996</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>40000</v>
+      </c>
+      <c r="H12">
+        <v>7.7135699999999998</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12">
+        <v>40000</v>
+      </c>
+      <c r="L12">
+        <v>7.8226500000000003</v>
+      </c>
+      <c r="O12">
+        <v>40000</v>
+      </c>
+      <c r="P12">
+        <v>7.6532600000000004</v>
+      </c>
+      <c r="Q12">
+        <v>7.7135699999999998</v>
+      </c>
+      <c r="R12">
+        <v>7.8226500000000003</v>
+      </c>
+      <c r="S12">
+        <v>1000000</v>
+      </c>
+      <c r="T12">
+        <v>152.18700000000001</v>
+      </c>
+      <c r="U12">
+        <v>151.23500000000001</v>
+      </c>
+      <c r="V12">
+        <v>151.697</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13">
+        <v>40000</v>
+      </c>
+      <c r="D13">
+        <v>7.6532600000000004</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13">
+        <v>80000</v>
+      </c>
+      <c r="H13">
+        <v>10.548500000000001</v>
+      </c>
+      <c r="J13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13">
+        <v>80000</v>
+      </c>
+      <c r="L13">
+        <v>10.6911</v>
+      </c>
+      <c r="O13">
+        <v>80000</v>
+      </c>
+      <c r="P13">
+        <v>10.9232</v>
+      </c>
+      <c r="Q13">
+        <v>10.548500000000001</v>
+      </c>
+      <c r="R13">
+        <v>10.6911</v>
+      </c>
+      <c r="S13">
+        <v>1200000</v>
+      </c>
+      <c r="T13">
+        <v>180.57599999999999</v>
+      </c>
+      <c r="U13">
+        <v>179.84100000000001</v>
+      </c>
+      <c r="V13">
+        <v>180.08</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14">
+        <v>60000</v>
+      </c>
+      <c r="D14">
+        <v>9.4447200000000002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14">
+        <v>100000</v>
+      </c>
+      <c r="H14">
+        <v>12.061299999999999</v>
+      </c>
+      <c r="J14" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14">
+        <v>100000</v>
+      </c>
+      <c r="L14">
+        <v>12.233599999999999</v>
+      </c>
+      <c r="O14">
+        <v>100000</v>
+      </c>
+      <c r="P14">
+        <v>13.191000000000001</v>
+      </c>
+      <c r="Q14">
+        <v>12.061299999999999</v>
+      </c>
+      <c r="R14">
+        <v>12.233599999999999</v>
+      </c>
+      <c r="S14">
+        <v>1400000</v>
+      </c>
+      <c r="T14">
+        <v>209.34700000000001</v>
+      </c>
+      <c r="U14">
+        <v>208.619</v>
+      </c>
+      <c r="V14">
+        <v>209.053</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>80000</v>
+      </c>
+      <c r="D15">
+        <v>10.9232</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15">
+        <v>150000</v>
+      </c>
+      <c r="H15">
+        <v>21.8507</v>
+      </c>
+      <c r="J15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15">
+        <v>150000</v>
+      </c>
+      <c r="L15">
+        <v>22.024799999999999</v>
+      </c>
+      <c r="O15">
+        <v>150000</v>
+      </c>
+      <c r="P15">
+        <v>23.0747</v>
+      </c>
+      <c r="Q15">
+        <v>21.8507</v>
+      </c>
+      <c r="R15">
+        <v>22.024799999999999</v>
+      </c>
+      <c r="S15">
+        <v>1600000</v>
+      </c>
+      <c r="T15">
+        <v>238.00299999999999</v>
+      </c>
+      <c r="U15">
+        <v>237.40600000000001</v>
+      </c>
+      <c r="V15">
+        <v>237.44800000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16">
+        <v>100000</v>
+      </c>
+      <c r="D16">
+        <v>13.191000000000001</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16">
+        <v>200000</v>
+      </c>
+      <c r="H16">
+        <v>29.034800000000001</v>
+      </c>
+      <c r="J16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16">
+        <v>200000</v>
+      </c>
+      <c r="L16">
+        <v>29.699200000000001</v>
+      </c>
+      <c r="O16">
+        <v>200000</v>
+      </c>
+      <c r="P16">
+        <v>30.912700000000001</v>
+      </c>
+      <c r="Q16">
+        <v>29.034800000000001</v>
+      </c>
+      <c r="R16">
+        <v>29.699200000000001</v>
+      </c>
+      <c r="S16">
+        <v>1800000</v>
+      </c>
+      <c r="T16">
+        <v>267.29599999999999</v>
+      </c>
+      <c r="U16">
+        <v>266.38499999999999</v>
+      </c>
+      <c r="V16">
+        <v>266.49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17">
+        <v>150000</v>
+      </c>
+      <c r="D17">
+        <v>23.0747</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17">
+        <v>250000</v>
+      </c>
+      <c r="H17">
+        <v>37.765799999999999</v>
+      </c>
+      <c r="J17" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17">
+        <v>250000</v>
+      </c>
+      <c r="L17">
+        <v>38.727499999999999</v>
+      </c>
+      <c r="O17">
+        <v>250000</v>
+      </c>
+      <c r="P17">
+        <v>41.323999999999998</v>
+      </c>
+      <c r="Q17">
+        <v>37.765799999999999</v>
+      </c>
+      <c r="R17">
+        <v>38.727499999999999</v>
+      </c>
+      <c r="S17">
+        <v>2000000</v>
+      </c>
+      <c r="T17">
+        <v>296.84699999999998</v>
+      </c>
+      <c r="U17">
+        <v>294.94799999999998</v>
+      </c>
+      <c r="V17">
+        <v>295.24200000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18">
+        <v>200000</v>
+      </c>
+      <c r="D18">
+        <v>30.912700000000001</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18">
+        <v>300000</v>
+      </c>
+      <c r="H18">
+        <v>47.618600000000001</v>
+      </c>
+      <c r="J18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18">
+        <v>300000</v>
+      </c>
+      <c r="L18">
+        <v>47.109400000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>250000</v>
+      </c>
+      <c r="D19">
+        <v>41.323999999999998</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19">
+        <v>350000</v>
+      </c>
+      <c r="H19">
+        <v>56.924599999999998</v>
+      </c>
+      <c r="J19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19">
+        <v>350000</v>
+      </c>
+      <c r="L19">
+        <v>55.116900000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20">
+        <v>300000</v>
+      </c>
+      <c r="D20">
+        <v>49.077300000000001</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20">
+        <v>400000</v>
+      </c>
+      <c r="H20">
+        <v>64.066100000000006</v>
+      </c>
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20">
+        <v>400000</v>
+      </c>
+      <c r="L20">
+        <v>62.265799999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>350000</v>
+      </c>
+      <c r="D21">
+        <v>58.703600000000002</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21">
+        <v>500000</v>
+      </c>
+      <c r="H21">
+        <v>79.241900000000001</v>
+      </c>
+      <c r="J21" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21">
+        <v>500000</v>
+      </c>
+      <c r="L21">
+        <v>79.390100000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22">
+        <v>400000</v>
+      </c>
+      <c r="D22">
+        <v>64.316400000000002</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22">
+        <v>600000</v>
+      </c>
+      <c r="H22">
+        <v>93.808400000000006</v>
+      </c>
+      <c r="J22" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22">
+        <v>600000</v>
+      </c>
+      <c r="L22">
+        <v>94.276300000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>500000</v>
+      </c>
+      <c r="D23">
+        <v>78.499799999999993</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23">
+        <v>700000</v>
+      </c>
+      <c r="H23">
+        <v>108.27200000000001</v>
+      </c>
+      <c r="J23" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23">
+        <v>700000</v>
+      </c>
+      <c r="L23">
+        <v>108.879</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24">
+        <v>600000</v>
+      </c>
+      <c r="D24">
+        <v>92.214299999999994</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24">
+        <v>800000</v>
+      </c>
+      <c r="H24">
+        <v>122.247</v>
+      </c>
+      <c r="J24" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24">
+        <v>800000</v>
+      </c>
+      <c r="L24">
+        <v>122.502</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>700000</v>
+      </c>
+      <c r="D25">
+        <v>108.71599999999999</v>
+      </c>
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25">
+        <v>900000</v>
+      </c>
+      <c r="H25">
+        <v>136.72999999999999</v>
+      </c>
+      <c r="J25" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25">
+        <v>900000</v>
+      </c>
+      <c r="L25">
+        <v>137.17400000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26">
+        <v>800000</v>
+      </c>
+      <c r="D26">
+        <v>123.306</v>
+      </c>
+      <c r="F26" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26">
+        <v>1000000</v>
+      </c>
+      <c r="H26">
+        <v>151.23500000000001</v>
+      </c>
+      <c r="J26" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26">
+        <v>1000000</v>
+      </c>
+      <c r="L26">
+        <v>151.697</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27">
+        <v>900000</v>
+      </c>
+      <c r="D27">
+        <v>137.59899999999999</v>
+      </c>
+      <c r="F27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27">
+        <v>1200000</v>
+      </c>
+      <c r="H27">
+        <v>179.84100000000001</v>
+      </c>
+      <c r="J27" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27">
+        <v>1200000</v>
+      </c>
+      <c r="L27">
+        <v>180.08</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28">
+        <v>1000000</v>
+      </c>
+      <c r="D28">
+        <v>152.18700000000001</v>
+      </c>
+      <c r="F28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28">
+        <v>1400000</v>
+      </c>
+      <c r="H28">
+        <v>208.619</v>
+      </c>
+      <c r="J28" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28">
+        <v>1400000</v>
+      </c>
+      <c r="L28">
+        <v>209.053</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29">
+        <v>1200000</v>
+      </c>
+      <c r="D29">
+        <v>180.57599999999999</v>
+      </c>
+      <c r="F29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29">
+        <v>1600000</v>
+      </c>
+      <c r="H29">
+        <v>237.40600000000001</v>
+      </c>
+      <c r="J29" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29">
+        <v>1600000</v>
+      </c>
+      <c r="L29">
+        <v>237.44800000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30">
+        <v>1400000</v>
+      </c>
+      <c r="D30">
+        <v>209.34700000000001</v>
+      </c>
+      <c r="F30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30">
+        <v>1800000</v>
+      </c>
+      <c r="H30">
+        <v>266.38499999999999</v>
+      </c>
+      <c r="J30" t="s">
+        <v>69</v>
+      </c>
+      <c r="K30">
+        <v>1800000</v>
+      </c>
+      <c r="L30">
+        <v>266.49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31">
+        <v>1500000</v>
+      </c>
+      <c r="D31">
+        <v>227.02</v>
+      </c>
+      <c r="F31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31">
+        <v>2000000</v>
+      </c>
+      <c r="H31">
+        <v>294.94799999999998</v>
+      </c>
+      <c r="J31" t="s">
+        <v>69</v>
+      </c>
+      <c r="K31">
+        <v>2000000</v>
+      </c>
+      <c r="L31">
+        <v>295.24200000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32">
+        <v>1600000</v>
+      </c>
+      <c r="D32">
+        <v>238.00299999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33">
+        <v>1800000</v>
+      </c>
+      <c r="D33">
+        <v>267.29599999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34">
+        <v>2000000</v>
+      </c>
+      <c r="D34">
+        <v>296.84699999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35">
+        <v>200</v>
+      </c>
+      <c r="D35">
+        <v>4.2739500000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36">
+        <v>400</v>
+      </c>
+      <c r="D36">
+        <v>4.4763099999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37">
+        <v>1000</v>
+      </c>
+      <c r="D37">
+        <v>4.4807300000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38">
+        <v>2000</v>
+      </c>
+      <c r="D38">
+        <v>4.4973900000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39">
+        <v>4000</v>
+      </c>
+      <c r="D39">
+        <v>4.5514799999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40">
+        <v>10000</v>
+      </c>
+      <c r="D40">
+        <v>4.7199299999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41">
+        <v>20000</v>
+      </c>
+      <c r="D41">
+        <v>6.194</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42">
+        <v>40000</v>
+      </c>
+      <c r="D42">
+        <v>7.7135699999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43">
+        <v>80000</v>
+      </c>
+      <c r="D43">
+        <v>10.548500000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44">
+        <v>100000</v>
+      </c>
+      <c r="D44">
+        <v>12.061299999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45">
+        <v>150000</v>
+      </c>
+      <c r="D45">
+        <v>21.8507</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46">
+        <v>200000</v>
+      </c>
+      <c r="D46">
+        <v>29.034800000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47">
+        <v>250000</v>
+      </c>
+      <c r="D47">
+        <v>37.765799999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48">
+        <v>300000</v>
+      </c>
+      <c r="D48">
+        <v>47.618600000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49">
+        <v>350000</v>
+      </c>
+      <c r="D49">
+        <v>56.924599999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50">
+        <v>400000</v>
+      </c>
+      <c r="D50">
+        <v>64.066100000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51">
+        <v>500000</v>
+      </c>
+      <c r="D51">
+        <v>79.241900000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52">
+        <v>600000</v>
+      </c>
+      <c r="D52">
+        <v>93.808400000000006</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53">
+        <v>700000</v>
+      </c>
+      <c r="D53">
+        <v>108.27200000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54">
+        <v>800000</v>
+      </c>
+      <c r="D54">
+        <v>122.247</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55">
+        <v>900000</v>
+      </c>
+      <c r="D55">
+        <v>136.72999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56">
+        <v>1000000</v>
+      </c>
+      <c r="D56">
+        <v>151.23500000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57">
+        <v>1200000</v>
+      </c>
+      <c r="D57">
+        <v>179.84100000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58">
+        <v>1400000</v>
+      </c>
+      <c r="D58">
+        <v>208.619</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59">
+        <v>1600000</v>
+      </c>
+      <c r="D59">
+        <v>237.40600000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60">
+        <v>1800000</v>
+      </c>
+      <c r="D60">
+        <v>266.38499999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61">
+        <v>2000000</v>
+      </c>
+      <c r="D61">
+        <v>294.94799999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62">
+        <v>200</v>
+      </c>
+      <c r="D62">
+        <v>4.4091699999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63">
+        <v>400</v>
+      </c>
+      <c r="D63">
+        <v>4.4284499999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64">
+        <v>1000</v>
+      </c>
+      <c r="D64">
+        <v>4.4563800000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65">
+        <v>2000</v>
+      </c>
+      <c r="D65">
+        <v>4.5598000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66">
+        <v>4000</v>
+      </c>
+      <c r="D66">
+        <v>4.5202</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67">
+        <v>10000</v>
+      </c>
+      <c r="D67">
+        <v>4.6811100000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68">
+        <v>20000</v>
+      </c>
+      <c r="D68">
+        <v>6.2668900000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69">
+        <v>40000</v>
+      </c>
+      <c r="D69">
+        <v>7.8226500000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70">
+        <v>80000</v>
+      </c>
+      <c r="D70">
+        <v>10.6911</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71">
+        <v>100000</v>
+      </c>
+      <c r="D71">
+        <v>12.233599999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72">
+        <v>150000</v>
+      </c>
+      <c r="D72">
+        <v>22.024799999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73">
+        <v>200000</v>
+      </c>
+      <c r="D73">
+        <v>29.699200000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74">
+        <v>250000</v>
+      </c>
+      <c r="D74">
+        <v>38.727499999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75">
+        <v>300000</v>
+      </c>
+      <c r="D75">
+        <v>47.109400000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76">
+        <v>350000</v>
+      </c>
+      <c r="D76">
+        <v>55.116900000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77">
+        <v>400000</v>
+      </c>
+      <c r="D77">
+        <v>62.265799999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78">
+        <v>500000</v>
+      </c>
+      <c r="D78">
+        <v>79.390100000000004</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79">
+        <v>600000</v>
+      </c>
+      <c r="D79">
+        <v>94.276300000000006</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80">
+        <v>700000</v>
+      </c>
+      <c r="D80">
+        <v>108.879</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81">
+        <v>800000</v>
+      </c>
+      <c r="D81">
+        <v>122.502</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>69</v>
+      </c>
+      <c r="C82">
+        <v>900000</v>
+      </c>
+      <c r="D82">
+        <v>137.17400000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>69</v>
+      </c>
+      <c r="C83">
+        <v>1000000</v>
+      </c>
+      <c r="D83">
+        <v>151.697</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84">
+        <v>1200000</v>
+      </c>
+      <c r="D84">
+        <v>180.08</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85">
+        <v>1400000</v>
+      </c>
+      <c r="D85">
+        <v>209.053</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86">
+        <v>1600000</v>
+      </c>
+      <c r="D86">
+        <v>237.44800000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87">
+        <v>1800000</v>
+      </c>
+      <c r="D87">
+        <v>266.49</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88">
+        <v>2000000</v>
+      </c>
+      <c r="D88">
+        <v>295.24200000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Memoria/library/mediciones auxiliares.xlsx
+++ b/Memoria/library/mediciones auxiliares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\TFG\Memoria\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60552AEB-2B91-4A02-BCF4-54C1E2C1E491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091BBE06-EEB2-43B8-87C1-AC2F835B5339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Euler" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="77">
   <si>
     <t>Runge Kutta</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Adams Bashford Moulton</t>
-  </si>
-  <si>
-    <t>Comparativa de métodos y tecnologías para Brusselator1D, neqn=100K</t>
   </si>
   <si>
     <t>Speedup</t>
@@ -268,6 +265,15 @@
   <si>
     <t>Grid2</t>
   </si>
+  <si>
+    <t>Comparativa de métodos y tecnologías para Brusselator1D, neqn=100K, y para simpleadvdiff</t>
+  </si>
+  <si>
+    <t>t(s)</t>
+  </si>
+  <si>
+    <t>OMP Componentes</t>
+  </si>
 </sst>
 </file>
 
@@ -432,6 +438,201 @@
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F071A7C7-C907-4782-97BC-1691119DD71E}"/>
   </cellStyles>
   <dxfs count="32">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -850,201 +1051,6 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3679,7 +3685,7 @@
     <tableColumn id="7" xr3:uid="{64FA0956-3E24-4150-B966-D174B7BC073B}" name="Hebras"/>
     <tableColumn id="10" xr3:uid="{1B8321A3-89E7-440F-AC38-60832AF9D3BF}" name="T (s)"/>
     <tableColumn id="4" xr3:uid="{2A319FA1-3453-4EE4-B2DC-4F5247C2B6CA}" name="Speedup"/>
-    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="22">
+    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="31">
       <calculatedColumnFormula>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3688,6 +3694,20 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}" name="Tabla9" displayName="Tabla9" ref="C3:E18" totalsRowShown="0">
+  <autoFilter ref="C3:E18" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}"/>
+  <tableColumns count="3">
+    <tableColumn id="10" xr3:uid="{386D6B24-9F12-4906-A98F-C1ECE9B2AF91}" name="T - CON"/>
+    <tableColumn id="12" xr3:uid="{BF967619-27A5-4370-8EB3-0CF9D0A5FB92}" name="T - SIN"/>
+    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="0">
+      <calculatedColumnFormula>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}" name="Tabla10" displayName="Tabla10" ref="B4:D88" totalsRowShown="0">
   <autoFilter ref="B4:D88" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}"/>
   <tableColumns count="3">
@@ -3699,7 +3719,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}" name="Tabla11" displayName="Tabla11" ref="J4:L31" totalsRowShown="0">
   <autoFilter ref="J4:L31" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}"/>
   <tableColumns count="3">
@@ -3711,7 +3731,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}" name="Tabla12" displayName="Tabla12" ref="F4:H31" totalsRowShown="0">
   <autoFilter ref="F4:H31" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}"/>
   <tableColumns count="3">
@@ -3723,7 +3743,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}" name="Tabla13" displayName="Tabla13" ref="O4:V17" totalsRowShown="0">
   <autoFilter ref="O4:V17" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}"/>
   <tableColumns count="8">
@@ -3741,18 +3761,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="30">
   <autoFilter ref="A17:F23" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:D23">
     <sortCondition descending="1" ref="D17:D23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="26"/>
     <tableColumn id="5" xr3:uid="{BF613CE6-6DEF-4C0B-848D-8F065FCF2C50}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="16">
+    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="25">
       <calculatedColumnFormula>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3761,18 +3781,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="24">
   <autoFilter ref="A9:F15" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:D15">
     <sortCondition descending="1" ref="D9:D15"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{417AEB65-89EB-4AD8-BE23-D32970ABEDB3}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="19">
       <calculatedColumnFormula>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3781,6 +3801,19 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{186076A2-FBD2-4EE7-8A1E-C4B2122C78FB}" name="Tabla14" displayName="Tabla14" ref="I4:L22" totalsRowShown="0">
+  <autoFilter ref="I4:L22" xr:uid="{186076A2-FBD2-4EE7-8A1E-C4B2122C78FB}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{036D236A-CB03-49C4-B738-BE410D43089B}" name="Solver"/>
+    <tableColumn id="2" xr3:uid="{FF42F9BC-7ED9-4788-ADC6-2835BD825437}" name="Tipo"/>
+    <tableColumn id="3" xr3:uid="{DE7EDE9F-AF7A-4557-A422-5F385DE6F3CA}" name="Hebras"/>
+    <tableColumn id="4" xr3:uid="{0498710B-FE7B-4168-BB94-20B57A6B5FCD}" name="t(s)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8C8ECA13-2EB2-4FC1-85DE-E2A3D0878827}" name="Tabla2" displayName="Tabla2" ref="C3:H21" totalsRowShown="0">
   <autoFilter ref="C3:H21" xr:uid="{8C8ECA13-2EB2-4FC1-85DE-E2A3D0878827}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:F21">
@@ -3792,7 +3825,7 @@
     <tableColumn id="3" xr3:uid="{3A3C5E88-C7DA-483A-917E-BB271E1A560D}" name="Tipo"/>
     <tableColumn id="10" xr3:uid="{16A7936E-BB2A-4361-A80F-5CD098124D72}" name="T (s)"/>
     <tableColumn id="1" xr3:uid="{99669171-F1C7-4284-B05F-40B0C07B15FF}" name="Speedup"/>
-    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="18">
       <calculatedColumnFormula>Tabla2[[#This Row],[Speedup]]/Tabla2[[#This Row],[Hebras]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3800,15 +3833,15 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="K3:O12" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="10">
       <calculatedColumnFormula>Tabla3[[#This Row],[Speedup]]/Tabla3[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3816,7 +3849,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED7CDD12-53B9-478E-8FA6-1644F23C7700}" name="Tabla6" displayName="Tabla6" ref="D3:G12" totalsRowShown="0">
   <autoFilter ref="D3:G12" xr:uid="{ED7CDD12-53B9-478E-8FA6-1644F23C7700}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D4:F12">
@@ -3832,14 +3865,14 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}" name="Tabla7" displayName="Tabla7" ref="B3:E29" totalsRowShown="0">
   <autoFilter ref="B3:E29" xr:uid="{BF881151-CBB8-40EC-B240-A88C073513E6}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{644F7757-56D6-4333-9A04-BB025A3FA537}" name="Solver"/>
     <tableColumn id="9" xr3:uid="{7A4B951A-072B-4FA9-BB96-812FB6E68533}" name="neqn"/>
     <tableColumn id="10" xr3:uid="{27844286-B464-4C11-8051-BCFF52593894}" name="T (s)"/>
-    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="31">
+    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="9">
       <calculatedColumnFormula>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3847,33 +3880,19 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="30">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="H3:P12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{932C3C52-A732-48FA-B5C5-2E96D1AF7393}" name="neqn"/>
     <tableColumn id="2" xr3:uid="{180E0420-BB3F-4A15-AA9C-8504B61074B7}" name="T (s)"/>
-    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="23"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}" name="Tabla9" displayName="Tabla9" ref="C3:E18" totalsRowShown="0">
-  <autoFilter ref="C3:E18" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}"/>
-  <tableColumns count="3">
-    <tableColumn id="10" xr3:uid="{386D6B24-9F12-4906-A98F-C1ECE9B2AF91}" name="T - CON"/>
-    <tableColumn id="12" xr3:uid="{BF967619-27A5-4370-8EB3-0CF9D0A5FB92}" name="T - SIN"/>
-    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="0">
-      <calculatedColumnFormula>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4151,12 +4170,12 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2">
         <v>0.1</v>
@@ -4164,19 +4183,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4416,15 +4435,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -4438,16 +4460,16 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
       <c r="H1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4468,7 +4490,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -4489,7 +4511,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4510,8 +4532,20 @@
         <f>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</f>
         <v>93.282068414207814</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -4532,8 +4566,20 @@
         <f>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</f>
         <v>103.84144865969402</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1568.93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -4554,8 +4600,20 @@
         <f>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</f>
         <v>79.34691599218533</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>345.55799999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -4576,8 +4634,34 @@
         <f>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</f>
         <v>53.544047757684645</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>432.42099999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>98.190899999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4591,13 +4675,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <v>134.35499999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -4617,8 +4713,20 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>16</v>
+      </c>
+      <c r="L10">
+        <v>78.525400000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -4638,8 +4746,20 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>294.63900000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
@@ -4660,8 +4780,20 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>98.523883514610802</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>175.83199999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
@@ -4682,8 +4814,20 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>106.12227370928218</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>72.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>7</v>
       </c>
@@ -4704,8 +4848,20 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>78.253997883837542</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <v>40.6982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
@@ -4726,8 +4882,34 @@
         <f>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</f>
         <v>52.538133895704362</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15">
+        <v>16</v>
+      </c>
+      <c r="L15">
+        <v>34.569200000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>16</v>
+      </c>
+      <c r="L16">
+        <v>39.700499999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -4741,13 +4923,25 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="I17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1367.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -4767,8 +4961,20 @@
         <f>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>561.56399999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>8</v>
       </c>
@@ -4788,8 +4994,20 @@
         <f>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <v>359.767</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -4810,8 +5028,20 @@
         <f>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</f>
         <v>56.4164826142027</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>138.93100000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>8</v>
       </c>
@@ -4832,8 +5062,20 @@
         <f>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</f>
         <v>101.17906113447393</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21">
+        <v>16</v>
+      </c>
+      <c r="L21">
+        <v>150.57900000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
@@ -4854,8 +5096,20 @@
         <f>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</f>
         <v>76.770599740342945</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>16</v>
+      </c>
+      <c r="L22">
+        <v>139.524</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>8</v>
       </c>
@@ -4879,10 +5133,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4901,15 +5156,15 @@
   <sheetData>
     <row r="1" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
         <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -4921,25 +5176,25 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" t="s">
         <v>6</v>
       </c>
       <c r="N3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.25">
@@ -4950,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>976.06100000000004</v>
@@ -4988,7 +5243,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>2151.79</v>
@@ -5026,7 +5281,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>263.08100000000002</v>
@@ -5065,7 +5320,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>569.69299999999998</v>
@@ -5104,7 +5359,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8">
         <v>180.66200000000001</v>
@@ -5143,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>206.744</v>
@@ -5182,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>1825.86</v>
@@ -5220,7 +5475,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>3970.37</v>
@@ -5258,7 +5513,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12">
         <v>466.28199999999998</v>
@@ -5297,7 +5552,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>1049.3499999999999</v>
@@ -5319,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14">
         <v>214.67</v>
@@ -5341,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15">
         <v>331.80900000000003</v>
@@ -5363,7 +5618,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16">
         <v>2692.79</v>
@@ -5384,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>5982.94</v>
@@ -5405,7 +5660,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18">
         <v>675.12300000000005</v>
@@ -5427,7 +5682,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19">
         <v>1593.61</v>
@@ -5449,7 +5704,7 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20">
         <v>264.40199999999999</v>
@@ -5471,7 +5726,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21">
         <v>445.08100000000002</v>
@@ -5508,7 +5763,7 @@
   <sheetData>
     <row r="1" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="4:7" x14ac:dyDescent="0.25">
@@ -5522,7 +5777,7 @@
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="4:7" x14ac:dyDescent="0.25">
@@ -5530,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>2531.0100000000002</v>
@@ -5545,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>236.42</v>
@@ -5560,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>77.1447</v>
@@ -5575,7 +5830,7 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>847.87</v>
@@ -5589,7 +5844,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>82.703999999999994</v>
@@ -5604,7 +5859,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>23.554400000000001</v>
@@ -5619,7 +5874,7 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>2692.79</v>
@@ -5633,7 +5888,7 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <v>264.40199999999999</v>
@@ -5648,7 +5903,7 @@
         <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12">
         <v>86.291600000000003</v>
@@ -5678,7 +5933,7 @@
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="H1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
@@ -5697,40 +5952,40 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
         <v>6</v>
       </c>
       <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
         <v>30</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>34</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>35</v>
-      </c>
-      <c r="P3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
@@ -5757,7 +6012,7 @@
         <v>94.21</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L4">
         <v>33.409999999999997</v>
@@ -5766,7 +6021,7 @@
         <v>0.55600000000000005</v>
       </c>
       <c r="N4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O4">
         <v>246.38</v>
@@ -5799,7 +6054,7 @@
         <v>47.91</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L5">
         <v>38.56</v>
@@ -5808,7 +6063,7 @@
         <v>0.48199999999999998</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O5">
         <v>291.95</v>
@@ -5832,7 +6087,7 @@
         <v>17.084399999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6">
         <v>17.079999999999998</v>
@@ -5841,7 +6096,7 @@
         <v>17.084</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L6">
         <v>43.4</v>
@@ -5850,7 +6105,7 @@
         <v>0.434</v>
       </c>
       <c r="N6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O6">
         <v>335.23</v>
@@ -5874,7 +6129,7 @@
         <v>8.5485500000000005</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>17.09</v>
@@ -5883,7 +6138,7 @@
         <v>8.548</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>68.540000000000006</v>
@@ -5892,7 +6147,7 @@
         <v>0.45600000000000002</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O7">
         <v>379.27</v>
@@ -5916,7 +6171,7 @@
         <v>4.3003749999999998</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>17.2</v>
@@ -5925,7 +6180,7 @@
         <v>4.3003</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L8">
         <v>89.16</v>
@@ -5934,7 +6189,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="N8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O8">
         <v>423.52</v>
@@ -5958,7 +6213,7 @@
         <v>1.74387</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9">
         <v>17.43</v>
@@ -5967,7 +6222,7 @@
         <v>1.7430000000000001</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L9">
         <v>115.64</v>
@@ -5976,7 +6231,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="N9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O9">
         <v>469.07</v>
@@ -6000,7 +6255,7 @@
         <v>1.1150899999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10">
         <v>22.3</v>
@@ -6009,7 +6264,7 @@
         <v>1.115</v>
       </c>
       <c r="K10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L10">
         <v>141.37</v>
@@ -6018,7 +6273,7 @@
         <v>0.47099999999999997</v>
       </c>
       <c r="N10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O10">
         <v>702.06</v>
@@ -6042,7 +6297,7 @@
         <v>0.7860166666666667</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11">
         <v>23.58</v>
@@ -6051,7 +6306,7 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L11">
         <v>173.56</v>
@@ -6060,7 +6315,7 @@
         <v>0.495</v>
       </c>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O11">
         <v>927.77</v>
@@ -6084,7 +6339,7 @@
         <v>0.70684499999999995</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I12">
         <v>28.27</v>
@@ -6093,7 +6348,7 @@
         <v>0.70599999999999996</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L12">
         <v>195.79</v>
@@ -6378,21 +6633,21 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -6646,7 +6901,7 @@
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
@@ -6654,16 +6909,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
         <v>6</v>
@@ -6672,39 +6927,39 @@
         <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L4" t="s">
         <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R4" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>72</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>73</v>
-      </c>
-      <c r="V4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -6713,7 +6968,7 @@
         <v>4.2511799999999997</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>200</v>
@@ -6722,7 +6977,7 @@
         <v>4.2739500000000001</v>
       </c>
       <c r="J5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K5">
         <v>200</v>
@@ -6757,7 +7012,7 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6">
         <v>400</v>
@@ -6766,7 +7021,7 @@
         <v>4.3825000000000003</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>400</v>
@@ -6775,7 +7030,7 @@
         <v>4.4763099999999998</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K6">
         <v>400</v>
@@ -6810,7 +7065,7 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -6819,7 +7074,7 @@
         <v>4.4242800000000004</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -6828,7 +7083,7 @@
         <v>4.4807300000000003</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -6863,7 +7118,7 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -6872,7 +7127,7 @@
         <v>4.4725599999999996</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>2000</v>
@@ -6881,7 +7136,7 @@
         <v>4.4973900000000002</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K8">
         <v>2000</v>
@@ -6916,7 +7171,7 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>4000</v>
@@ -6925,7 +7180,7 @@
         <v>4.5078199999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>4000</v>
@@ -6934,7 +7189,7 @@
         <v>4.5514799999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K9">
         <v>4000</v>
@@ -6969,7 +7224,7 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -6978,7 +7233,7 @@
         <v>4.64262</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>10000</v>
@@ -6987,7 +7242,7 @@
         <v>4.7199299999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K10">
         <v>10000</v>
@@ -7022,7 +7277,7 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11">
         <v>20000</v>
@@ -7031,7 +7286,7 @@
         <v>6.0775300000000003</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>20000</v>
@@ -7040,7 +7295,7 @@
         <v>6.194</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K11">
         <v>20000</v>
@@ -7075,7 +7330,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>30000</v>
@@ -7084,7 +7339,7 @@
         <v>6.4583899999999996</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>40000</v>
@@ -7093,7 +7348,7 @@
         <v>7.7135699999999998</v>
       </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K12">
         <v>40000</v>
@@ -7128,7 +7383,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>40000</v>
@@ -7137,7 +7392,7 @@
         <v>7.6532600000000004</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <v>80000</v>
@@ -7146,7 +7401,7 @@
         <v>10.548500000000001</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K13">
         <v>80000</v>
@@ -7181,7 +7436,7 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>60000</v>
@@ -7190,7 +7445,7 @@
         <v>9.4447200000000002</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>100000</v>
@@ -7199,7 +7454,7 @@
         <v>12.061299999999999</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K14">
         <v>100000</v>
@@ -7234,7 +7489,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>80000</v>
@@ -7243,7 +7498,7 @@
         <v>10.9232</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>150000</v>
@@ -7252,7 +7507,7 @@
         <v>21.8507</v>
       </c>
       <c r="J15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K15">
         <v>150000</v>
@@ -7287,7 +7542,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <v>100000</v>
@@ -7296,7 +7551,7 @@
         <v>13.191000000000001</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>200000</v>
@@ -7305,7 +7560,7 @@
         <v>29.034800000000001</v>
       </c>
       <c r="J16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K16">
         <v>200000</v>
@@ -7340,7 +7595,7 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>150000</v>
@@ -7349,7 +7604,7 @@
         <v>23.0747</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>250000</v>
@@ -7358,7 +7613,7 @@
         <v>37.765799999999999</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K17">
         <v>250000</v>
@@ -7393,7 +7648,7 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>200000</v>
@@ -7402,7 +7657,7 @@
         <v>30.912700000000001</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18">
         <v>300000</v>
@@ -7411,7 +7666,7 @@
         <v>47.618600000000001</v>
       </c>
       <c r="J18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K18">
         <v>300000</v>
@@ -7422,7 +7677,7 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19">
         <v>250000</v>
@@ -7431,7 +7686,7 @@
         <v>41.323999999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>350000</v>
@@ -7440,7 +7695,7 @@
         <v>56.924599999999998</v>
       </c>
       <c r="J19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K19">
         <v>350000</v>
@@ -7451,7 +7706,7 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20">
         <v>300000</v>
@@ -7460,7 +7715,7 @@
         <v>49.077300000000001</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20">
         <v>400000</v>
@@ -7469,7 +7724,7 @@
         <v>64.066100000000006</v>
       </c>
       <c r="J20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K20">
         <v>400000</v>
@@ -7480,7 +7735,7 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21">
         <v>350000</v>
@@ -7489,7 +7744,7 @@
         <v>58.703600000000002</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>500000</v>
@@ -7498,7 +7753,7 @@
         <v>79.241900000000001</v>
       </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K21">
         <v>500000</v>
@@ -7509,7 +7764,7 @@
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22">
         <v>400000</v>
@@ -7518,7 +7773,7 @@
         <v>64.316400000000002</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22">
         <v>600000</v>
@@ -7527,7 +7782,7 @@
         <v>93.808400000000006</v>
       </c>
       <c r="J22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K22">
         <v>600000</v>
@@ -7538,7 +7793,7 @@
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>500000</v>
@@ -7547,7 +7802,7 @@
         <v>78.499799999999993</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G23">
         <v>700000</v>
@@ -7556,7 +7811,7 @@
         <v>108.27200000000001</v>
       </c>
       <c r="J23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K23">
         <v>700000</v>
@@ -7567,7 +7822,7 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <v>600000</v>
@@ -7576,7 +7831,7 @@
         <v>92.214299999999994</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G24">
         <v>800000</v>
@@ -7585,7 +7840,7 @@
         <v>122.247</v>
       </c>
       <c r="J24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K24">
         <v>800000</v>
@@ -7596,7 +7851,7 @@
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>700000</v>
@@ -7605,7 +7860,7 @@
         <v>108.71599999999999</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G25">
         <v>900000</v>
@@ -7614,7 +7869,7 @@
         <v>136.72999999999999</v>
       </c>
       <c r="J25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K25">
         <v>900000</v>
@@ -7625,7 +7880,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26">
         <v>800000</v>
@@ -7634,7 +7889,7 @@
         <v>123.306</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G26">
         <v>1000000</v>
@@ -7643,7 +7898,7 @@
         <v>151.23500000000001</v>
       </c>
       <c r="J26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K26">
         <v>1000000</v>
@@ -7654,7 +7909,7 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>900000</v>
@@ -7663,7 +7918,7 @@
         <v>137.59899999999999</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G27">
         <v>1200000</v>
@@ -7672,7 +7927,7 @@
         <v>179.84100000000001</v>
       </c>
       <c r="J27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K27">
         <v>1200000</v>
@@ -7683,7 +7938,7 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28">
         <v>1000000</v>
@@ -7692,7 +7947,7 @@
         <v>152.18700000000001</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G28">
         <v>1400000</v>
@@ -7701,7 +7956,7 @@
         <v>208.619</v>
       </c>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K28">
         <v>1400000</v>
@@ -7712,7 +7967,7 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29">
         <v>1200000</v>
@@ -7721,7 +7976,7 @@
         <v>180.57599999999999</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G29">
         <v>1600000</v>
@@ -7730,7 +7985,7 @@
         <v>237.40600000000001</v>
       </c>
       <c r="J29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K29">
         <v>1600000</v>
@@ -7741,7 +7996,7 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C30">
         <v>1400000</v>
@@ -7750,7 +8005,7 @@
         <v>209.34700000000001</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30">
         <v>1800000</v>
@@ -7759,7 +8014,7 @@
         <v>266.38499999999999</v>
       </c>
       <c r="J30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K30">
         <v>1800000</v>
@@ -7770,7 +8025,7 @@
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C31">
         <v>1500000</v>
@@ -7779,7 +8034,7 @@
         <v>227.02</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31">
         <v>2000000</v>
@@ -7788,7 +8043,7 @@
         <v>294.94799999999998</v>
       </c>
       <c r="J31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K31">
         <v>2000000</v>
@@ -7799,7 +8054,7 @@
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32">
         <v>1600000</v>
@@ -7810,7 +8065,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C33">
         <v>1800000</v>
@@ -7821,7 +8076,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C34">
         <v>2000000</v>
@@ -7832,7 +8087,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -7843,7 +8098,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36">
         <v>400</v>
@@ -7854,7 +8109,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37">
         <v>1000</v>
@@ -7865,7 +8120,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38">
         <v>2000</v>
@@ -7876,7 +8131,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>4000</v>
@@ -7887,7 +8142,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40">
         <v>10000</v>
@@ -7898,7 +8153,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41">
         <v>20000</v>
@@ -7909,7 +8164,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>40000</v>
@@ -7920,7 +8175,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>80000</v>
@@ -7931,7 +8186,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>100000</v>
@@ -7942,7 +8197,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>150000</v>
@@ -7953,7 +8208,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>200000</v>
@@ -7964,7 +8219,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>250000</v>
@@ -7975,7 +8230,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>300000</v>
@@ -7986,7 +8241,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49">
         <v>350000</v>
@@ -7997,7 +8252,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <v>400000</v>
@@ -8008,7 +8263,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51">
         <v>500000</v>
@@ -8019,7 +8274,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52">
         <v>600000</v>
@@ -8030,7 +8285,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C53">
         <v>700000</v>
@@ -8041,7 +8296,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54">
         <v>800000</v>
@@ -8052,7 +8307,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C55">
         <v>900000</v>
@@ -8063,7 +8318,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56">
         <v>1000000</v>
@@ -8074,7 +8329,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57">
         <v>1200000</v>
@@ -8085,7 +8340,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58">
         <v>1400000</v>
@@ -8096,7 +8351,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59">
         <v>1600000</v>
@@ -8107,7 +8362,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60">
         <v>1800000</v>
@@ -8118,7 +8373,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C61">
         <v>2000000</v>
@@ -8129,7 +8384,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -8140,7 +8395,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63">
         <v>400</v>
@@ -8151,7 +8406,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64">
         <v>1000</v>
@@ -8162,7 +8417,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65">
         <v>2000</v>
@@ -8173,7 +8428,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C66">
         <v>4000</v>
@@ -8184,7 +8439,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67">
         <v>10000</v>
@@ -8195,7 +8450,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68">
         <v>20000</v>
@@ -8206,7 +8461,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69">
         <v>40000</v>
@@ -8217,7 +8472,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C70">
         <v>80000</v>
@@ -8228,7 +8483,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C71">
         <v>100000</v>
@@ -8239,7 +8494,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C72">
         <v>150000</v>
@@ -8250,7 +8505,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C73">
         <v>200000</v>
@@ -8261,7 +8516,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C74">
         <v>250000</v>
@@ -8272,7 +8527,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C75">
         <v>300000</v>
@@ -8283,7 +8538,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C76">
         <v>350000</v>
@@ -8294,7 +8549,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77">
         <v>400000</v>
@@ -8305,7 +8560,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C78">
         <v>500000</v>
@@ -8316,7 +8571,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C79">
         <v>600000</v>
@@ -8327,7 +8582,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80">
         <v>700000</v>
@@ -8338,7 +8593,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C81">
         <v>800000</v>
@@ -8349,7 +8604,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C82">
         <v>900000</v>
@@ -8360,7 +8615,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C83">
         <v>1000000</v>
@@ -8371,7 +8626,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C84">
         <v>1200000</v>
@@ -8382,7 +8637,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C85">
         <v>1400000</v>
@@ -8393,7 +8648,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C86">
         <v>1600000</v>
@@ -8404,7 +8659,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C87">
         <v>1800000</v>
@@ -8415,7 +8670,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C88">
         <v>2000000</v>

--- a/Memoria/library/mediciones auxiliares.xlsx
+++ b/Memoria/library/mediciones auxiliares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Google Drive\Uni\TFG\Memoria\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091BBE06-EEB2-43B8-87C1-AC2F835B5339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E93D6E-65F4-430F-8426-1278B3BD327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Euler" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="81">
   <si>
     <t>Runge Kutta</t>
   </si>
@@ -221,9 +221,6 @@
     <t>2M</t>
   </si>
   <si>
-    <t>Comparo RK y BR1D a través de distintos tamaños</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
@@ -273,6 +270,21 @@
   </si>
   <si>
     <t>OMP Componentes</t>
+  </si>
+  <si>
+    <t>Comparo RK con ADV1D y BR1D a través de distintos tamaños</t>
+  </si>
+  <si>
+    <t>T (s)2</t>
+  </si>
+  <si>
+    <t>ms/eq2</t>
+  </si>
+  <si>
+    <t>neqn3</t>
+  </si>
+  <si>
+    <t>ms/eq3</t>
   </si>
 </sst>
 </file>
@@ -437,7 +449,10 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{894E2A58-4AB2-4DD0-992A-D8EFC287A90D}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{F071A7C7-C907-4782-97BC-1691119DD71E}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3685,7 +3700,7 @@
     <tableColumn id="7" xr3:uid="{64FA0956-3E24-4150-B966-D174B7BC073B}" name="Hebras"/>
     <tableColumn id="10" xr3:uid="{1B8321A3-89E7-440F-AC38-60832AF9D3BF}" name="T (s)"/>
     <tableColumn id="4" xr3:uid="{2A319FA1-3453-4EE4-B2DC-4F5247C2B6CA}" name="Speedup"/>
-    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="31">
+    <tableColumn id="5" xr3:uid="{C8FBE361-944A-4D70-9B75-2CFCB1A1B454}" name="Efficiency" dataDxfId="32">
       <calculatedColumnFormula>Table1[[#This Row],[Speedup]]/Table1[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3694,12 +3709,44 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{E84F1AA3-4E90-4357-A9A3-E087AD695B92}" name="Tabla15" displayName="Tabla15" ref="G3:I29" totalsRowShown="0">
+  <autoFilter ref="G3:I29" xr:uid="{E84F1AA3-4E90-4357-A9A3-E087AD695B92}"/>
+  <tableColumns count="3">
+    <tableColumn id="9" xr3:uid="{1FB7F42F-A28A-415D-87DF-10147636C809}" name="neqn"/>
+    <tableColumn id="10" xr3:uid="{6B290550-A14F-4ED6-A0CB-28CFE477FCEE}" name="T (s)"/>
+    <tableColumn id="11" xr3:uid="{597C480E-1843-4915-8605-CF9C315F2D63}" name="ms/eq" dataDxfId="0">
+      <calculatedColumnFormula>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{E949A7C6-6E1E-413C-873F-68AF25297DF2}" name="Tabla16" displayName="Tabla16" ref="M16:U25" totalsRowShown="0">
+  <autoFilter ref="M16:U25" xr:uid="{E949A7C6-6E1E-413C-873F-68AF25297DF2}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{E9B488FF-B52A-4052-8C3A-D4301FA7AB57}" name="neqn"/>
+    <tableColumn id="2" xr3:uid="{E70D4405-9CF2-4D72-BD7C-66B32DEFA8C8}" name="T (s)"/>
+    <tableColumn id="3" xr3:uid="{4E0AC869-9315-49EA-9D67-7CB514E7A481}" name="ms/eq"/>
+    <tableColumn id="4" xr3:uid="{7818AC8C-7334-41E5-823B-0321E63884E6}" name="neqn2"/>
+    <tableColumn id="5" xr3:uid="{C41A331F-1D98-48F7-9BE1-5B17DCF6221C}" name="T (s)2"/>
+    <tableColumn id="6" xr3:uid="{83C4B073-6F44-40D0-AB4C-F2C0392CC93A}" name="ms/eq2"/>
+    <tableColumn id="7" xr3:uid="{FE1D5C32-8FE7-4AD5-93A6-3DE319C4F0C0}" name="neqn3"/>
+    <tableColumn id="8" xr3:uid="{2C959683-0077-4596-BC4C-35B0D421A327}" name="T (s)3"/>
+    <tableColumn id="9" xr3:uid="{BA17556A-55CB-4776-92DE-26CF356532EE}" name="ms/eq3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}" name="Tabla9" displayName="Tabla9" ref="C3:E18" totalsRowShown="0">
   <autoFilter ref="C3:E18" xr:uid="{E1C59661-95E7-4C50-B593-60AF4BF0419B}"/>
   <tableColumns count="3">
     <tableColumn id="10" xr3:uid="{386D6B24-9F12-4906-A98F-C1ECE9B2AF91}" name="T - CON"/>
     <tableColumn id="12" xr3:uid="{BF967619-27A5-4370-8EB3-0CF9D0A5FB92}" name="T - SIN"/>
-    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{E8BDDCA8-85C9-47C8-B35D-4CDC5658DC19}" name="Sin/Con" dataDxfId="1">
       <calculatedColumnFormula>Tabla9[[#This Row],[T - SIN]]/Tabla9[[#This Row],[T - CON]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3707,7 +3754,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}" name="Tabla10" displayName="Tabla10" ref="B4:D88" totalsRowShown="0">
   <autoFilter ref="B4:D88" xr:uid="{304C16FE-1A89-449E-B4E2-DA6D14937524}"/>
   <tableColumns count="3">
@@ -3719,7 +3766,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}" name="Tabla11" displayName="Tabla11" ref="J4:L31" totalsRowShown="0">
   <autoFilter ref="J4:L31" xr:uid="{A1DF3A69-E8A4-411B-83EC-4E166FFEA468}"/>
   <tableColumns count="3">
@@ -3731,7 +3778,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}" name="Tabla12" displayName="Tabla12" ref="F4:H31" totalsRowShown="0">
   <autoFilter ref="F4:H31" xr:uid="{973BEA52-9B7C-4998-849D-398358C1B573}"/>
   <tableColumns count="3">
@@ -3743,7 +3790,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}" name="Tabla13" displayName="Tabla13" ref="O4:V17" totalsRowShown="0">
   <autoFilter ref="O4:V17" xr:uid="{816A0534-7E92-45A4-95E2-DE17D1227A63}"/>
   <tableColumns count="8">
@@ -3761,18 +3808,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}" name="Table5" displayName="Table5" ref="A17:F23" totalsRowShown="0" tableBorderDxfId="31">
   <autoFilter ref="A17:F23" xr:uid="{4C862F51-80EA-4323-A23D-AD6AF32D6737}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:D23">
     <sortCondition descending="1" ref="D17:D23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{969FCA7D-D340-4C13-86B2-C6EAC19CA12B}" name="Solver" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{F8648533-FD1A-4D6C-8084-2704645141D9}" name="Tipo" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{DC1BAEBC-A405-45AC-8E1D-FF0D7620EE8C}" name="Hebras" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{3D2F94AF-2C19-468F-80BC-25BE9607F57F}" name="T (s)" dataDxfId="27"/>
     <tableColumn id="5" xr3:uid="{BF613CE6-6DEF-4C0B-848D-8F065FCF2C50}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="25">
+    <tableColumn id="6" xr3:uid="{0B73B7C0-235F-4E05-B847-5F924635199C}" name="Effiency" dataDxfId="26">
       <calculatedColumnFormula>Table5[[#This Row],[Speedup]]/Table5[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3781,18 +3828,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}" name="Table4" displayName="Table4" ref="A9:F15" totalsRowShown="0" tableBorderDxfId="25">
   <autoFilter ref="A9:F15" xr:uid="{92F64B1B-7B7C-4525-B20C-2EFC812E8E5A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:D15">
     <sortCondition descending="1" ref="D9:D15"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{7672D6E0-6AC8-4B4D-A458-0BEE8A35C91C}" name="Solver" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{6C7C42B2-536F-4E04-830E-69EE87657A05}" name="Tipo" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{64021EE0-9E33-4FD5-83BD-34DA6D8320B7}" name="Hebras" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{397664F5-F154-4BCD-AD93-987F3D8C8EFE}" name="T (s)" dataDxfId="21"/>
     <tableColumn id="5" xr3:uid="{417AEB65-89EB-4AD8-BE23-D32970ABEDB3}" name="Speedup"/>
-    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="19">
+    <tableColumn id="6" xr3:uid="{BD17F5F8-C972-4C88-8F9D-3540C6C6AE0F}" name="Efficiency" dataDxfId="20">
       <calculatedColumnFormula>Table4[[#This Row],[Speedup]]/Table4[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3825,7 +3872,7 @@
     <tableColumn id="3" xr3:uid="{3A3C5E88-C7DA-483A-917E-BB271E1A560D}" name="Tipo"/>
     <tableColumn id="10" xr3:uid="{16A7936E-BB2A-4361-A80F-5CD098124D72}" name="T (s)"/>
     <tableColumn id="1" xr3:uid="{99669171-F1C7-4284-B05F-40B0C07B15FF}" name="Speedup"/>
-    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{0F99AB6F-95B0-48AC-AFFA-9572A938E9D5}" name="Effiency" dataDxfId="19">
       <calculatedColumnFormula>Tabla2[[#This Row],[Speedup]]/Tabla2[[#This Row],[Hebras]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3834,14 +3881,14 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}" name="Tabla3" displayName="Tabla3" ref="K3:O12" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="K3:O12" xr:uid="{500B26C9-CF13-4F25-BA27-B1B312614597}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="10">
+    <tableColumn id="1" xr3:uid="{9B87CB8C-71FB-48E7-ABD0-361458E1F0C5}" name="Hebras" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7EE98D31-1E21-441D-ABE1-C50ADAD61A70}" name="neqn" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{147E8177-E9F7-4A21-8C6F-F807667557B0}" name="T (s)" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{9CC0064A-ACE5-4E3E-870C-8D7A7547540E}" name="Speedup" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{A4DD618E-02AE-479D-AF72-8E73365EF307}" name="Eficiencia" dataDxfId="11">
       <calculatedColumnFormula>Tabla3[[#This Row],[Speedup]]/Tabla3[[#This Row],[Hebras]]*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3872,7 +3919,7 @@
     <tableColumn id="1" xr3:uid="{644F7757-56D6-4333-9A04-BB025A3FA537}" name="Solver"/>
     <tableColumn id="9" xr3:uid="{7A4B951A-072B-4FA9-BB96-812FB6E68533}" name="neqn"/>
     <tableColumn id="10" xr3:uid="{27844286-B464-4C11-8051-BCFF52593894}" name="T (s)"/>
-    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{C4C270E6-294F-4C6C-9E30-CC46609C7C96}" name="ms/eq" dataDxfId="10">
       <calculatedColumnFormula>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3881,18 +3928,18 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="H3:P12" totalsRowShown="0" dataDxfId="8">
-  <autoFilter ref="H3:P12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}" name="Tabla8" displayName="Tabla8" ref="M3:U12" totalsRowShown="0" dataDxfId="9">
+  <autoFilter ref="M3:U12" xr:uid="{0C13DA08-D36E-4DC6-AD4D-C5ED3A2D2FFE}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{932C3C52-A732-48FA-B5C5-2E96D1AF7393}" name="neqn"/>
     <tableColumn id="2" xr3:uid="{180E0420-BB3F-4A15-AA9C-8504B61074B7}" name="T (s)"/>
-    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{9CD8DE62-128C-4DC7-8194-28F682AB47BE}" name="ms/eq" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{1C3E6784-B380-4E71-BD53-644073AFAABA}" name="neqn2" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{61BCB526-EF0F-4CEE-92F7-BCE6C4B0BDFD}" name="T (s)3" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{B376E533-C766-4D62-969F-995271FAC762}" name="ms/eq4" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{93F3FE3F-20CE-4AD5-AA05-7DFC7DFBB20D}" name="neqn5" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{0DB727DE-811B-4C13-9A70-3781C9DD0690}" name="T (s)6" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{10AD593B-05BC-4C4D-9C4F-32785D7D5748}" name="ms/eq7" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4466,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4542,7 +4589,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -4570,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -4638,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -4684,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K9">
         <v>16</v>
@@ -4750,7 +4797,7 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -4818,7 +4865,7 @@
         <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -4886,7 +4933,7 @@
         <v>7</v>
       </c>
       <c r="J15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K15">
         <v>16</v>
@@ -4932,7 +4979,7 @@
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -4998,7 +5045,7 @@
         <v>8</v>
       </c>
       <c r="J19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -5066,7 +5113,7 @@
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K21">
         <v>16</v>
@@ -5923,7 +5970,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61388887-C6C4-4F6F-8AD6-C9DE40C79BFF}">
-  <dimension ref="B1:R29"/>
+  <dimension ref="B1:U29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
@@ -5931,23 +5978,21 @@
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="H1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
+    <row r="1" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="O2" s="14"/>
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -5960,35 +6005,44 @@
       <c r="E3" t="s">
         <v>29</v>
       </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
       <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" t="s">
+      <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
+      <c r="R3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
+      <c r="S3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" t="s">
+      <c r="T3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" t="s">
+      <c r="U3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -6002,35 +6056,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>94.21</v>
       </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
       <c r="H4">
+        <v>21.426300000000001</v>
+      </c>
+      <c r="I4">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>214.26300000000001</v>
+      </c>
+      <c r="M4">
         <v>200</v>
       </c>
-      <c r="I4">
+      <c r="N4">
         <v>18.84</v>
       </c>
-      <c r="J4">
+      <c r="O4">
         <v>94.21</v>
       </c>
-      <c r="K4" t="s">
+      <c r="P4" t="s">
         <v>42</v>
       </c>
-      <c r="L4">
+      <c r="Q4">
         <v>33.409999999999997</v>
       </c>
-      <c r="M4">
+      <c r="R4">
         <v>0.55600000000000005</v>
       </c>
-      <c r="N4" t="s">
+      <c r="S4" t="s">
         <v>51</v>
       </c>
-      <c r="O4">
+      <c r="T4">
         <v>246.38</v>
       </c>
-      <c r="P4">
+      <c r="U4">
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -6044,35 +6108,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>47.91075</v>
       </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
       <c r="H5">
+        <v>28.723600000000001</v>
+      </c>
+      <c r="I5">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>143.61799999999999</v>
+      </c>
+      <c r="M5">
         <v>400</v>
       </c>
-      <c r="I5">
+      <c r="N5">
         <v>19.16</v>
       </c>
-      <c r="J5">
+      <c r="O5">
         <v>47.91</v>
       </c>
-      <c r="K5" t="s">
+      <c r="P5" t="s">
         <v>43</v>
       </c>
-      <c r="L5">
+      <c r="Q5">
         <v>38.56</v>
       </c>
-      <c r="M5">
+      <c r="R5">
         <v>0.48199999999999998</v>
       </c>
-      <c r="N5" t="s">
+      <c r="S5" t="s">
         <v>52</v>
       </c>
-      <c r="O5">
+      <c r="T5">
         <v>291.95</v>
       </c>
-      <c r="P5">
+      <c r="U5">
         <v>0.48599999999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>0</v>
       </c>
@@ -6086,35 +6160,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>17.084399999999999</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G6">
+        <v>500</v>
+      </c>
+      <c r="H6">
+        <v>31.041499999999999</v>
+      </c>
+      <c r="I6">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>62.082999999999998</v>
+      </c>
+      <c r="M6" t="s">
         <v>36</v>
       </c>
-      <c r="I6">
+      <c r="N6">
         <v>17.079999999999998</v>
       </c>
-      <c r="J6">
+      <c r="O6">
         <v>17.084</v>
       </c>
-      <c r="K6" t="s">
+      <c r="P6" t="s">
         <v>44</v>
       </c>
-      <c r="L6">
+      <c r="Q6">
         <v>43.4</v>
       </c>
-      <c r="M6">
+      <c r="R6">
         <v>0.434</v>
       </c>
-      <c r="N6" t="s">
+      <c r="S6" t="s">
         <v>53</v>
       </c>
-      <c r="O6">
+      <c r="T6">
         <v>335.23</v>
       </c>
-      <c r="P6">
+      <c r="U6">
         <v>0.47799999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>0</v>
       </c>
@@ -6128,35 +6212,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>8.5485500000000005</v>
       </c>
-      <c r="H7" t="s">
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>30.878</v>
+      </c>
+      <c r="I7">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>30.878</v>
+      </c>
+      <c r="M7" t="s">
         <v>37</v>
       </c>
-      <c r="I7">
+      <c r="N7">
         <v>17.09</v>
       </c>
-      <c r="J7">
+      <c r="O7">
         <v>8.548</v>
       </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
         <v>45</v>
       </c>
-      <c r="L7">
+      <c r="Q7">
         <v>68.540000000000006</v>
       </c>
-      <c r="M7">
+      <c r="R7">
         <v>0.45600000000000002</v>
       </c>
-      <c r="N7" t="s">
+      <c r="S7" t="s">
         <v>54</v>
       </c>
-      <c r="O7">
+      <c r="T7">
         <v>379.27</v>
       </c>
-      <c r="P7">
+      <c r="U7">
         <v>0.47399999999999998</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>0</v>
       </c>
@@ -6170,35 +6264,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>4.3003749999999998</v>
       </c>
-      <c r="H8" t="s">
+      <c r="G8">
+        <v>2000</v>
+      </c>
+      <c r="H8">
+        <v>31.2256</v>
+      </c>
+      <c r="I8">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>15.6128</v>
+      </c>
+      <c r="M8" t="s">
         <v>38</v>
       </c>
-      <c r="I8">
+      <c r="N8">
         <v>17.2</v>
       </c>
-      <c r="J8">
+      <c r="O8">
         <v>4.3003</v>
       </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
         <v>46</v>
       </c>
-      <c r="L8">
+      <c r="Q8">
         <v>89.16</v>
       </c>
-      <c r="M8">
+      <c r="R8">
         <v>0.44500000000000001</v>
       </c>
-      <c r="N8" t="s">
+      <c r="S8" t="s">
         <v>55</v>
       </c>
-      <c r="O8">
+      <c r="T8">
         <v>423.52</v>
       </c>
-      <c r="P8">
+      <c r="U8">
         <v>0.47</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -6212,35 +6316,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>1.74387</v>
       </c>
-      <c r="H9" t="s">
-        <v>60</v>
+      <c r="G9">
+        <v>5000</v>
+      </c>
+      <c r="H9">
+        <v>31.218399999999999</v>
       </c>
       <c r="I9">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>6.2436799999999995</v>
+      </c>
+      <c r="M9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9">
         <v>17.43</v>
       </c>
-      <c r="J9">
+      <c r="O9">
         <v>1.7430000000000001</v>
       </c>
-      <c r="K9" t="s">
+      <c r="P9" t="s">
         <v>47</v>
       </c>
-      <c r="L9">
+      <c r="Q9">
         <v>115.64</v>
       </c>
-      <c r="M9">
+      <c r="R9">
         <v>0.46200000000000002</v>
       </c>
-      <c r="N9" t="s">
+      <c r="S9" t="s">
         <v>56</v>
       </c>
-      <c r="O9">
+      <c r="T9">
         <v>469.07</v>
       </c>
-      <c r="P9">
+      <c r="U9">
         <v>0.46899999999999997</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>0</v>
       </c>
@@ -6254,35 +6368,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>1.1150899999999999</v>
       </c>
-      <c r="H10" t="s">
+      <c r="G10">
+        <v>10000</v>
+      </c>
+      <c r="H10">
+        <v>31.145700000000001</v>
+      </c>
+      <c r="I10">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>3.1145700000000001</v>
+      </c>
+      <c r="M10" t="s">
         <v>39</v>
       </c>
-      <c r="I10">
+      <c r="N10">
         <v>22.3</v>
       </c>
-      <c r="J10">
+      <c r="O10">
         <v>1.115</v>
       </c>
-      <c r="K10" t="s">
+      <c r="P10" t="s">
         <v>48</v>
       </c>
-      <c r="L10">
+      <c r="Q10">
         <v>141.37</v>
       </c>
-      <c r="M10">
+      <c r="R10">
         <v>0.47099999999999997</v>
       </c>
-      <c r="N10" t="s">
+      <c r="S10" t="s">
         <v>57</v>
       </c>
-      <c r="O10">
+      <c r="T10">
         <v>702.06</v>
       </c>
-      <c r="P10">
+      <c r="U10">
         <v>0.46800000000000003</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>0</v>
       </c>
@@ -6296,35 +6420,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.7860166666666667</v>
       </c>
-      <c r="H11" t="s">
+      <c r="G11">
+        <v>15000</v>
+      </c>
+      <c r="H11">
+        <v>32.794499999999999</v>
+      </c>
+      <c r="I11">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>2.1863000000000001</v>
+      </c>
+      <c r="M11" t="s">
         <v>40</v>
       </c>
-      <c r="I11">
+      <c r="N11">
         <v>23.58</v>
       </c>
-      <c r="J11">
+      <c r="O11">
         <v>0.78600000000000003</v>
       </c>
-      <c r="K11" t="s">
+      <c r="P11" t="s">
         <v>50</v>
       </c>
-      <c r="L11">
+      <c r="Q11">
         <v>173.56</v>
       </c>
-      <c r="M11">
+      <c r="R11">
         <v>0.495</v>
       </c>
-      <c r="N11" t="s">
+      <c r="S11" t="s">
         <v>58</v>
       </c>
-      <c r="O11">
+      <c r="T11">
         <v>927.77</v>
       </c>
-      <c r="P11">
+      <c r="U11">
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>0</v>
       </c>
@@ -6338,26 +6472,36 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.70684499999999995</v>
       </c>
-      <c r="H12" t="s">
+      <c r="G12">
+        <v>20000</v>
+      </c>
+      <c r="H12">
+        <v>51.704099999999997</v>
+      </c>
+      <c r="I12">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>2.5852049999999998</v>
+      </c>
+      <c r="M12" t="s">
         <v>41</v>
       </c>
-      <c r="I12">
+      <c r="N12">
         <v>28.27</v>
       </c>
-      <c r="J12">
+      <c r="O12">
         <v>0.70599999999999996</v>
       </c>
-      <c r="K12" t="s">
+      <c r="P12" t="s">
         <v>49</v>
       </c>
-      <c r="L12">
+      <c r="Q12">
         <v>195.79</v>
       </c>
-      <c r="M12">
+      <c r="R12">
         <v>0.48899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>0</v>
       </c>
@@ -6371,8 +6515,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.55684166666666657</v>
       </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>30000</v>
+      </c>
+      <c r="H13">
+        <v>53.405799999999999</v>
+      </c>
+      <c r="I13">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.7801933333333333</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>0</v>
       </c>
@@ -6386,8 +6540,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.48207250000000007</v>
       </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>40000</v>
+      </c>
+      <c r="H14">
+        <v>73.87</v>
+      </c>
+      <c r="I14">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.8467500000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>0</v>
       </c>
@@ -6401,8 +6565,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.43403700000000001</v>
       </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>50000</v>
+      </c>
+      <c r="H15">
+        <v>73.457300000000004</v>
+      </c>
+      <c r="I15">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.4691460000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>0</v>
       </c>
@@ -6416,8 +6590,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.45695600000000008</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>75000</v>
+      </c>
+      <c r="H16">
+        <v>115.03100000000001</v>
+      </c>
+      <c r="I16">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.5337466666666666</v>
+      </c>
+      <c r="M16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>77</v>
+      </c>
+      <c r="R16" t="s">
+        <v>78</v>
+      </c>
+      <c r="S16" t="s">
+        <v>79</v>
+      </c>
+      <c r="T16" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>0</v>
       </c>
@@ -6431,8 +6642,46 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.4458105</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>100000</v>
+      </c>
+      <c r="H17">
+        <v>134.52500000000001</v>
+      </c>
+      <c r="I17">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3452500000000001</v>
+      </c>
+      <c r="M17">
+        <v>50</v>
+      </c>
+      <c r="N17">
+        <v>27.43</v>
+      </c>
+      <c r="O17">
+        <f>Tabla16[[#This Row],[T (s)]]/Tabla16[[#This Row],[neqn]]*1000</f>
+        <v>548.6</v>
+      </c>
+      <c r="P17">
+        <v>20000</v>
+      </c>
+      <c r="Q17">
+        <v>51.704099999999997</v>
+      </c>
+      <c r="R17">
+        <v>2.5852049999999998</v>
+      </c>
+      <c r="S17">
+        <v>200000</v>
+      </c>
+      <c r="T17">
+        <v>270.13499999999999</v>
+      </c>
+      <c r="U17">
+        <v>1.3506750000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>0</v>
       </c>
@@ -6446,8 +6695,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.46257200000000004</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>125000</v>
+      </c>
+      <c r="H18">
+        <v>179.36500000000001</v>
+      </c>
+      <c r="I18">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.4349200000000002</v>
+      </c>
+      <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>21.426300000000001</v>
+      </c>
+      <c r="O18">
+        <v>214.26300000000001</v>
+      </c>
+      <c r="P18">
+        <v>30000</v>
+      </c>
+      <c r="Q18">
+        <v>53.405799999999999</v>
+      </c>
+      <c r="R18">
+        <v>1.7801933333333333</v>
+      </c>
+      <c r="S18">
+        <v>250000</v>
+      </c>
+      <c r="T18">
+        <v>340.20699999999999</v>
+      </c>
+      <c r="U18">
+        <v>1.3608279999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>0</v>
       </c>
@@ -6461,8 +6747,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.4712466666666667</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>150000</v>
+      </c>
+      <c r="H19">
+        <v>202.547</v>
+      </c>
+      <c r="I19">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3503133333333333</v>
+      </c>
+      <c r="M19">
+        <v>200</v>
+      </c>
+      <c r="N19">
+        <v>28.723600000000001</v>
+      </c>
+      <c r="O19">
+        <v>143.61799999999999</v>
+      </c>
+      <c r="P19">
+        <v>40000</v>
+      </c>
+      <c r="Q19">
+        <v>73.87</v>
+      </c>
+      <c r="R19">
+        <v>1.8467500000000001</v>
+      </c>
+      <c r="S19">
+        <v>300000</v>
+      </c>
+      <c r="T19">
+        <v>411.625</v>
+      </c>
+      <c r="U19">
+        <v>1.3720833333333333</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>0</v>
       </c>
@@ -6476,8 +6799,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.49589428571428568</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>175000</v>
+      </c>
+      <c r="H20">
+        <v>247.07400000000001</v>
+      </c>
+      <c r="I20">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.4118514285714285</v>
+      </c>
+      <c r="M20">
+        <v>500</v>
+      </c>
+      <c r="N20">
+        <v>31.041499999999999</v>
+      </c>
+      <c r="O20">
+        <v>62.082999999999998</v>
+      </c>
+      <c r="P20">
+        <v>50000</v>
+      </c>
+      <c r="Q20">
+        <v>73.457300000000004</v>
+      </c>
+      <c r="R20">
+        <v>1.4691460000000001</v>
+      </c>
+      <c r="S20">
+        <v>350000</v>
+      </c>
+      <c r="T20">
+        <v>484.81400000000002</v>
+      </c>
+      <c r="U20">
+        <v>1.385182857142857</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>0</v>
       </c>
@@ -6491,8 +6851,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.48948250000000004</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>200000</v>
+      </c>
+      <c r="H21">
+        <v>270.13499999999999</v>
+      </c>
+      <c r="I21">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3506750000000001</v>
+      </c>
+      <c r="M21">
+        <v>1000</v>
+      </c>
+      <c r="N21">
+        <v>30.878</v>
+      </c>
+      <c r="O21">
+        <v>30.878</v>
+      </c>
+      <c r="P21">
+        <v>75000</v>
+      </c>
+      <c r="Q21">
+        <v>115.03100000000001</v>
+      </c>
+      <c r="R21">
+        <v>1.5337466666666666</v>
+      </c>
+      <c r="S21">
+        <v>400000</v>
+      </c>
+      <c r="T21">
+        <v>542.48699999999997</v>
+      </c>
+      <c r="U21">
+        <v>1.3562175000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>0</v>
       </c>
@@ -6506,8 +6903,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.49277800000000005</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>250000</v>
+      </c>
+      <c r="H22">
+        <v>340.20699999999999</v>
+      </c>
+      <c r="I22">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3608279999999999</v>
+      </c>
+      <c r="M22">
+        <v>2000</v>
+      </c>
+      <c r="N22">
+        <v>31.2256</v>
+      </c>
+      <c r="O22">
+        <v>15.6128</v>
+      </c>
+      <c r="P22">
+        <v>100000</v>
+      </c>
+      <c r="Q22">
+        <v>134.52500000000001</v>
+      </c>
+      <c r="R22">
+        <v>1.3452500000000001</v>
+      </c>
+      <c r="S22">
+        <v>450000</v>
+      </c>
+      <c r="T22">
+        <v>615.779</v>
+      </c>
+      <c r="U22">
+        <v>1.3683977777777778</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>0</v>
       </c>
@@ -6521,8 +6955,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.48658500000000005</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>300000</v>
+      </c>
+      <c r="H23">
+        <v>411.625</v>
+      </c>
+      <c r="I23">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3720833333333333</v>
+      </c>
+      <c r="M23">
+        <v>5000</v>
+      </c>
+      <c r="N23">
+        <v>31.218399999999999</v>
+      </c>
+      <c r="O23">
+        <v>6.2436799999999995</v>
+      </c>
+      <c r="P23">
+        <v>125000</v>
+      </c>
+      <c r="Q23">
+        <v>179.36500000000001</v>
+      </c>
+      <c r="R23">
+        <v>1.4349200000000002</v>
+      </c>
+      <c r="S23">
+        <v>500000</v>
+      </c>
+      <c r="T23">
+        <v>687.30799999999999</v>
+      </c>
+      <c r="U23">
+        <v>1.3746159999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>0</v>
       </c>
@@ -6536,8 +7007,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.47890714285714286</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>350000</v>
+      </c>
+      <c r="H24">
+        <v>484.81400000000002</v>
+      </c>
+      <c r="I24">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.385182857142857</v>
+      </c>
+      <c r="M24">
+        <v>10000</v>
+      </c>
+      <c r="N24">
+        <v>31.145700000000001</v>
+      </c>
+      <c r="O24">
+        <v>3.1145700000000001</v>
+      </c>
+      <c r="P24">
+        <v>150000</v>
+      </c>
+      <c r="Q24">
+        <v>202.547</v>
+      </c>
+      <c r="R24">
+        <v>1.3503133333333333</v>
+      </c>
+      <c r="S24">
+        <v>750000</v>
+      </c>
+      <c r="T24">
+        <v>1044.07</v>
+      </c>
+      <c r="U24">
+        <v>1.3920933333333332</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>0</v>
       </c>
@@ -6551,8 +7059,45 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.47409125000000002</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>400000</v>
+      </c>
+      <c r="H25">
+        <v>542.48699999999997</v>
+      </c>
+      <c r="I25">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3562175000000001</v>
+      </c>
+      <c r="M25">
+        <v>15000</v>
+      </c>
+      <c r="N25">
+        <v>32.794499999999999</v>
+      </c>
+      <c r="O25">
+        <v>2.1863000000000001</v>
+      </c>
+      <c r="P25">
+        <v>175000</v>
+      </c>
+      <c r="Q25">
+        <v>247.07400000000001</v>
+      </c>
+      <c r="R25">
+        <v>1.4118514285714285</v>
+      </c>
+      <c r="S25">
+        <v>1000000</v>
+      </c>
+      <c r="T25">
+        <v>1375.45</v>
+      </c>
+      <c r="U25">
+        <v>1.3754500000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>0</v>
       </c>
@@ -6566,8 +7111,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.47057888888888888</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>450000</v>
+      </c>
+      <c r="H26">
+        <v>615.779</v>
+      </c>
+      <c r="I26">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3683977777777778</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>0</v>
       </c>
@@ -6581,8 +7136,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.46907100000000007</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>500000</v>
+      </c>
+      <c r="H27">
+        <v>687.30799999999999</v>
+      </c>
+      <c r="I27">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3746159999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>0</v>
       </c>
@@ -6596,8 +7161,18 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.46804533333333331</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>750000</v>
+      </c>
+      <c r="H28">
+        <v>1044.07</v>
+      </c>
+      <c r="I28">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3920933333333332</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>0</v>
       </c>
@@ -6611,12 +7186,24 @@
         <f>Tabla7[[#This Row],[T (s)]]/Tabla7[[#This Row],[neqn]]*1000</f>
         <v>0.46388749999999995</v>
       </c>
+      <c r="G29">
+        <v>1000000</v>
+      </c>
+      <c r="H29">
+        <v>1375.45</v>
+      </c>
+      <c r="I29">
+        <f>Tabla15[[#This Row],[T (s)]]/Tabla15[[#This Row],[neqn]]*1000</f>
+        <v>1.3754500000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
+  <tableParts count="4">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6633,7 +7220,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
@@ -6641,13 +7228,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
         <v>62</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -6901,7 +7488,7 @@
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
@@ -6915,7 +7502,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -6936,30 +7523,30 @@
         <v>12</v>
       </c>
       <c r="P4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="S4" t="s">
         <v>30</v>
       </c>
       <c r="T4" t="s">
+        <v>70</v>
+      </c>
+      <c r="U4" t="s">
         <v>71</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>72</v>
-      </c>
-      <c r="V4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -6968,7 +7555,7 @@
         <v>4.2511799999999997</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>200</v>
@@ -6977,7 +7564,7 @@
         <v>4.2739500000000001</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K5">
         <v>200</v>
@@ -7012,7 +7599,7 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>400</v>
@@ -7021,7 +7608,7 @@
         <v>4.3825000000000003</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>400</v>
@@ -7030,7 +7617,7 @@
         <v>4.4763099999999998</v>
       </c>
       <c r="J6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6">
         <v>400</v>
@@ -7065,7 +7652,7 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -7074,7 +7661,7 @@
         <v>4.4242800000000004</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -7083,7 +7670,7 @@
         <v>4.4807300000000003</v>
       </c>
       <c r="J7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -7118,7 +7705,7 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -7127,7 +7714,7 @@
         <v>4.4725599999999996</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>2000</v>
@@ -7136,7 +7723,7 @@
         <v>4.4973900000000002</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8">
         <v>2000</v>
@@ -7171,7 +7758,7 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>4000</v>
@@ -7180,7 +7767,7 @@
         <v>4.5078199999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>4000</v>
@@ -7189,7 +7776,7 @@
         <v>4.5514799999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K9">
         <v>4000</v>
@@ -7224,7 +7811,7 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -7233,7 +7820,7 @@
         <v>4.64262</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>10000</v>
@@ -7242,7 +7829,7 @@
         <v>4.7199299999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K10">
         <v>10000</v>
@@ -7277,7 +7864,7 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>20000</v>
@@ -7286,7 +7873,7 @@
         <v>6.0775300000000003</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>20000</v>
@@ -7295,7 +7882,7 @@
         <v>6.194</v>
       </c>
       <c r="J11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11">
         <v>20000</v>
@@ -7330,7 +7917,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>30000</v>
@@ -7339,7 +7926,7 @@
         <v>6.4583899999999996</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>40000</v>
@@ -7348,7 +7935,7 @@
         <v>7.7135699999999998</v>
       </c>
       <c r="J12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12">
         <v>40000</v>
@@ -7383,7 +7970,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>40000</v>
@@ -7392,7 +7979,7 @@
         <v>7.6532600000000004</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>80000</v>
@@ -7401,7 +7988,7 @@
         <v>10.548500000000001</v>
       </c>
       <c r="J13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13">
         <v>80000</v>
@@ -7436,7 +8023,7 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>60000</v>
@@ -7445,7 +8032,7 @@
         <v>9.4447200000000002</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>100000</v>
@@ -7454,7 +8041,7 @@
         <v>12.061299999999999</v>
       </c>
       <c r="J14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K14">
         <v>100000</v>
@@ -7489,7 +8076,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>80000</v>
@@ -7498,7 +8085,7 @@
         <v>10.9232</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>150000</v>
@@ -7507,7 +8094,7 @@
         <v>21.8507</v>
       </c>
       <c r="J15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K15">
         <v>150000</v>
@@ -7542,7 +8129,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <v>100000</v>
@@ -7551,7 +8138,7 @@
         <v>13.191000000000001</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>200000</v>
@@ -7560,7 +8147,7 @@
         <v>29.034800000000001</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K16">
         <v>200000</v>
@@ -7595,7 +8182,7 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17">
         <v>150000</v>
@@ -7604,7 +8191,7 @@
         <v>23.0747</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17">
         <v>250000</v>
@@ -7613,7 +8200,7 @@
         <v>37.765799999999999</v>
       </c>
       <c r="J17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K17">
         <v>250000</v>
@@ -7648,7 +8235,7 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>200000</v>
@@ -7657,7 +8244,7 @@
         <v>30.912700000000001</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18">
         <v>300000</v>
@@ -7666,7 +8253,7 @@
         <v>47.618600000000001</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K18">
         <v>300000</v>
@@ -7677,7 +8264,7 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19">
         <v>250000</v>
@@ -7686,7 +8273,7 @@
         <v>41.323999999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19">
         <v>350000</v>
@@ -7695,7 +8282,7 @@
         <v>56.924599999999998</v>
       </c>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K19">
         <v>350000</v>
@@ -7706,7 +8293,7 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20">
         <v>300000</v>
@@ -7715,7 +8302,7 @@
         <v>49.077300000000001</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20">
         <v>400000</v>
@@ -7724,7 +8311,7 @@
         <v>64.066100000000006</v>
       </c>
       <c r="J20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K20">
         <v>400000</v>
@@ -7735,7 +8322,7 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21">
         <v>350000</v>
@@ -7744,7 +8331,7 @@
         <v>58.703600000000002</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21">
         <v>500000</v>
@@ -7753,7 +8340,7 @@
         <v>79.241900000000001</v>
       </c>
       <c r="J21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K21">
         <v>500000</v>
@@ -7764,7 +8351,7 @@
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22">
         <v>400000</v>
@@ -7773,7 +8360,7 @@
         <v>64.316400000000002</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22">
         <v>600000</v>
@@ -7782,7 +8369,7 @@
         <v>93.808400000000006</v>
       </c>
       <c r="J22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K22">
         <v>600000</v>
@@ -7793,7 +8380,7 @@
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C23">
         <v>500000</v>
@@ -7802,7 +8389,7 @@
         <v>78.499799999999993</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23">
         <v>700000</v>
@@ -7811,7 +8398,7 @@
         <v>108.27200000000001</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K23">
         <v>700000</v>
@@ -7822,7 +8409,7 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24">
         <v>600000</v>
@@ -7831,7 +8418,7 @@
         <v>92.214299999999994</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24">
         <v>800000</v>
@@ -7840,7 +8427,7 @@
         <v>122.247</v>
       </c>
       <c r="J24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K24">
         <v>800000</v>
@@ -7851,7 +8438,7 @@
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25">
         <v>700000</v>
@@ -7860,7 +8447,7 @@
         <v>108.71599999999999</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25">
         <v>900000</v>
@@ -7869,7 +8456,7 @@
         <v>136.72999999999999</v>
       </c>
       <c r="J25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K25">
         <v>900000</v>
@@ -7880,7 +8467,7 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26">
         <v>800000</v>
@@ -7889,7 +8476,7 @@
         <v>123.306</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26">
         <v>1000000</v>
@@ -7898,7 +8485,7 @@
         <v>151.23500000000001</v>
       </c>
       <c r="J26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K26">
         <v>1000000</v>
@@ -7909,7 +8496,7 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27">
         <v>900000</v>
@@ -7918,7 +8505,7 @@
         <v>137.59899999999999</v>
       </c>
       <c r="F27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27">
         <v>1200000</v>
@@ -7927,7 +8514,7 @@
         <v>179.84100000000001</v>
       </c>
       <c r="J27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K27">
         <v>1200000</v>
@@ -7938,7 +8525,7 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28">
         <v>1000000</v>
@@ -7947,7 +8534,7 @@
         <v>152.18700000000001</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28">
         <v>1400000</v>
@@ -7956,7 +8543,7 @@
         <v>208.619</v>
       </c>
       <c r="J28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K28">
         <v>1400000</v>
@@ -7967,7 +8554,7 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29">
         <v>1200000</v>
@@ -7976,7 +8563,7 @@
         <v>180.57599999999999</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29">
         <v>1600000</v>
@@ -7985,7 +8572,7 @@
         <v>237.40600000000001</v>
       </c>
       <c r="J29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K29">
         <v>1600000</v>
@@ -7996,7 +8583,7 @@
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30">
         <v>1400000</v>
@@ -8005,7 +8592,7 @@
         <v>209.34700000000001</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30">
         <v>1800000</v>
@@ -8014,7 +8601,7 @@
         <v>266.38499999999999</v>
       </c>
       <c r="J30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K30">
         <v>1800000</v>
@@ -8025,7 +8612,7 @@
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C31">
         <v>1500000</v>
@@ -8034,7 +8621,7 @@
         <v>227.02</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31">
         <v>2000000</v>
@@ -8043,7 +8630,7 @@
         <v>294.94799999999998</v>
       </c>
       <c r="J31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K31">
         <v>2000000</v>
@@ -8054,7 +8641,7 @@
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32">
         <v>1600000</v>
@@ -8065,7 +8652,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33">
         <v>1800000</v>
@@ -8076,7 +8663,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>2000000</v>
@@ -8087,7 +8674,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -8098,7 +8685,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C36">
         <v>400</v>
@@ -8109,7 +8696,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37">
         <v>1000</v>
@@ -8120,7 +8707,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C38">
         <v>2000</v>
@@ -8131,7 +8718,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39">
         <v>4000</v>
@@ -8142,7 +8729,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C40">
         <v>10000</v>
@@ -8153,7 +8740,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41">
         <v>20000</v>
@@ -8164,7 +8751,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>40000</v>
@@ -8175,7 +8762,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>80000</v>
@@ -8186,7 +8773,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>100000</v>
@@ -8197,7 +8784,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>150000</v>
@@ -8208,7 +8795,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>200000</v>
@@ -8219,7 +8806,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>250000</v>
@@ -8230,7 +8817,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>300000</v>
@@ -8241,7 +8828,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>350000</v>
@@ -8252,7 +8839,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50">
         <v>400000</v>
@@ -8263,7 +8850,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51">
         <v>500000</v>
@@ -8274,7 +8861,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>600000</v>
@@ -8285,7 +8872,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>700000</v>
@@ -8296,7 +8883,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C54">
         <v>800000</v>
@@ -8307,7 +8894,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55">
         <v>900000</v>
@@ -8318,7 +8905,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56">
         <v>1000000</v>
@@ -8329,7 +8916,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57">
         <v>1200000</v>
@@ -8340,7 +8927,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58">
         <v>1400000</v>
@@ -8351,7 +8938,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59">
         <v>1600000</v>
@@ -8362,7 +8949,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60">
         <v>1800000</v>
@@ -8373,7 +8960,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C61">
         <v>2000000</v>
@@ -8384,7 +8971,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -8395,7 +8982,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63">
         <v>400</v>
@@ -8406,7 +8993,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64">
         <v>1000</v>
@@ -8417,7 +9004,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65">
         <v>2000</v>
@@ -8428,7 +9015,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66">
         <v>4000</v>
@@ -8439,7 +9026,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67">
         <v>10000</v>
@@ -8450,7 +9037,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68">
         <v>20000</v>
@@ -8461,7 +9048,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69">
         <v>40000</v>
@@ -8472,7 +9059,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70">
         <v>80000</v>
@@ -8483,7 +9070,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71">
         <v>100000</v>
@@ -8494,7 +9081,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72">
         <v>150000</v>
@@ -8505,7 +9092,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73">
         <v>200000</v>
@@ -8516,7 +9103,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74">
         <v>250000</v>
@@ -8527,7 +9114,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75">
         <v>300000</v>
@@ -8538,7 +9125,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C76">
         <v>350000</v>
@@ -8549,7 +9136,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C77">
         <v>400000</v>
@@ -8560,7 +9147,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C78">
         <v>500000</v>
@@ -8571,7 +9158,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C79">
         <v>600000</v>
@@ -8582,7 +9169,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C80">
         <v>700000</v>
@@ -8593,7 +9180,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81">
         <v>800000</v>
@@ -8604,7 +9191,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C82">
         <v>900000</v>
@@ -8615,7 +9202,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C83">
         <v>1000000</v>
@@ -8626,7 +9213,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C84">
         <v>1200000</v>
@@ -8637,7 +9224,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C85">
         <v>1400000</v>
@@ -8648,7 +9235,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C86">
         <v>1600000</v>
@@ -8659,7 +9246,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C87">
         <v>1800000</v>
@@ -8670,7 +9257,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C88">
         <v>2000000</v>
